--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FB06A7-7C7C-4F0C-BFAF-684F93A0FA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938408B1-AAB9-4B0F-88FA-5F1FB7B0EB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6504" yWindow="6384" windowWidth="22164" windowHeight="17904" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1248" yWindow="1848" windowWidth="22164" windowHeight="17904" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -19019,7 +19019,7 @@
         <v>420</v>
       </c>
       <c r="D454" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E454" s="4"/>
       <c r="F454" s="4" t="s">
@@ -19055,7 +19055,7 @@
         <v>311</v>
       </c>
       <c r="H455" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I455" s="4"/>
     </row>
@@ -19071,7 +19071,7 @@
         <v>235</v>
       </c>
       <c r="D456" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E456" s="4"/>
       <c r="F456" s="4" t="s">
@@ -19107,7 +19107,7 @@
         <v>413</v>
       </c>
       <c r="H457" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I457" s="4"/>
     </row>
@@ -19159,7 +19159,7 @@
         <v>319</v>
       </c>
       <c r="H459" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I459" s="4"/>
     </row>

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938408B1-AAB9-4B0F-88FA-5F1FB7B0EB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F8F8FB-833E-47E1-8AEB-A9DE65A9F590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1248" yWindow="1848" windowWidth="22164" windowHeight="17904" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3258" uniqueCount="428">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1470,13 +1470,53 @@
   </si>
   <si>
     <t>MIBR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EWC 2026</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026 电竞俱乐部世界杯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.07.06 - 08.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法国 巴黎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EWC.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1511,6 +1551,21 @@
       <color rgb="FFC9D1D9"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1578,7 +1633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1598,6 +1653,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1878,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -1964,20 +2020,20 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>62</v>
+      <c r="A4" s="17" t="s">
+        <v>423</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>424</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>427</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>425</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>72</v>
@@ -1988,22 +2044,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>340</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>80</v>
@@ -2011,16 +2067,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>53</v>
@@ -2031,19 +2090,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>53</v>
@@ -2054,131 +2110,154 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>339</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -17656,7 +17735,7 @@
         <v>50</v>
       </c>
       <c r="H401" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I401" s="4"/>
     </row>
@@ -17675,9 +17754,11 @@
       </c>
       <c r="E402" s="4"/>
       <c r="F402" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G402" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="G402" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="H402" s="4">
         <v>0</v>
       </c>
@@ -18967,7 +19048,7 @@
         <v>266</v>
       </c>
       <c r="D452" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E452" s="4"/>
       <c r="F452" s="4" t="s">
@@ -18977,7 +19058,7 @@
         <v>417</v>
       </c>
       <c r="H452" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I452" s="4"/>
     </row>
@@ -18993,7 +19074,7 @@
         <v>213</v>
       </c>
       <c r="D453" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E453" s="4"/>
       <c r="F453" s="4" t="s">
@@ -19123,7 +19204,7 @@
         <v>278</v>
       </c>
       <c r="D458" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E458" s="4"/>
       <c r="F458" s="4" t="s">
@@ -19133,7 +19214,7 @@
         <v>408</v>
       </c>
       <c r="H458" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I458" s="4"/>
     </row>
@@ -19169,17 +19250,21 @@
         <v>170</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C460" s="4"/>
+        <v>419</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>420</v>
+      </c>
       <c r="D460" s="4">
         <v>0</v>
       </c>
       <c r="E460" s="4"/>
       <c r="F460" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G460" s="4"/>
+        <v>421</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>235</v>
+      </c>
       <c r="H460" s="4">
         <v>0</v>
       </c>
@@ -19191,17 +19276,21 @@
         <v>170</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C461" s="4"/>
+        <v>310</v>
+      </c>
+      <c r="C461" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="D461" s="4">
         <v>0</v>
       </c>
       <c r="E461" s="4"/>
       <c r="F461" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G461" s="4"/>
+        <v>414</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>415</v>
+      </c>
       <c r="H461" s="4">
         <v>0</v>
       </c>
@@ -19213,17 +19302,21 @@
         <v>170</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C462" s="4"/>
+        <v>265</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="D462" s="4">
         <v>0</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G462" s="4"/>
+        <v>412</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>413</v>
+      </c>
       <c r="H462" s="4">
         <v>0</v>
       </c>
@@ -19235,19 +19328,23 @@
         <v>171</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C463" s="4"/>
+        <v>304</v>
+      </c>
+      <c r="C463" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="D463" s="4">
         <v>0</v>
       </c>
       <c r="E463" s="4"/>
       <c r="F463" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G463" s="4"/>
+        <v>418</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>319</v>
+      </c>
       <c r="H463" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I463" s="4"/>
     </row>
@@ -19257,19 +19354,23 @@
         <v>171</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C464" s="4"/>
+        <v>422</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>313</v>
+      </c>
       <c r="D464" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E464" s="4"/>
       <c r="F464" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G464" s="4"/>
+        <v>277</v>
+      </c>
+      <c r="G464" s="4" t="s">
+        <v>278</v>
+      </c>
       <c r="H464" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I464" s="4"/>
     </row>
@@ -19279,17 +19380,21 @@
         <v>171</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C465" s="4"/>
+        <v>279</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>280</v>
+      </c>
       <c r="D465" s="4">
         <v>0</v>
       </c>
       <c r="E465" s="4"/>
       <c r="F465" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G465" s="4"/>
+        <v>285</v>
+      </c>
+      <c r="G465" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="H465" s="4">
         <v>0</v>
       </c>

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F8F8FB-833E-47E1-8AEB-A9DE65A9F590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7A92A8-05C0-4237-BB7F-1CB747B7099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1248" yWindow="1848" windowWidth="22164" windowHeight="17904" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3258" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="428">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -19256,7 +19256,7 @@
         <v>420</v>
       </c>
       <c r="D460" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E460" s="4"/>
       <c r="F460" s="4" t="s">
@@ -19266,7 +19266,7 @@
         <v>235</v>
       </c>
       <c r="H460" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I460" s="4"/>
     </row>
@@ -19292,7 +19292,7 @@
         <v>415</v>
       </c>
       <c r="H461" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I461" s="4"/>
     </row>
@@ -19308,7 +19308,7 @@
         <v>266</v>
       </c>
       <c r="D462" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4" t="s">
@@ -19396,7 +19396,7 @@
         <v>286</v>
       </c>
       <c r="H465" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I465" s="4"/>
     </row>
@@ -19406,17 +19406,21 @@
         <v>172</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C466" s="4"/>
+        <v>419</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>420</v>
+      </c>
       <c r="D466" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E466" s="4"/>
       <c r="F466" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G466" s="4"/>
+        <v>418</v>
+      </c>
+      <c r="G466" s="4" t="s">
+        <v>319</v>
+      </c>
       <c r="H466" s="4">
         <v>0</v>
       </c>
@@ -19428,17 +19432,21 @@
         <v>172</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C467" s="4"/>
+        <v>285</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="D467" s="4">
         <v>0</v>
       </c>
       <c r="E467" s="4"/>
       <c r="F467" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G467" s="4"/>
+        <v>310</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="H467" s="4">
         <v>0</v>
       </c>
@@ -19450,17 +19458,21 @@
         <v>172</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C468" s="4"/>
+        <v>412</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>413</v>
+      </c>
       <c r="D468" s="4">
         <v>0</v>
       </c>
       <c r="E468" s="4"/>
       <c r="F468" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G468" s="4"/>
+        <v>277</v>
+      </c>
+      <c r="G468" s="4" t="s">
+        <v>278</v>
+      </c>
       <c r="H468" s="4">
         <v>0</v>
       </c>

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31560" windowHeight="17260" activeTab="2"/>
+    <workbookView windowWidth="31560" windowHeight="17260" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -7819,7 +7819,7 @@
         <v>133</v>
       </c>
       <c r="H174" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I174" s="14" t="s">
         <v>204</v>
@@ -7846,7 +7846,7 @@
         <v>135</v>
       </c>
       <c r="H175" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I175" s="14" t="s">
         <v>205</v>
@@ -7873,7 +7873,7 @@
         <v>136</v>
       </c>
       <c r="H176" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I176" s="14" t="s">
         <v>205</v>
@@ -7927,7 +7927,7 @@
         <v>139</v>
       </c>
       <c r="H178" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I178" s="14" t="s">
         <v>171</v>
@@ -19925,7 +19925,7 @@
         <v>263</v>
       </c>
       <c r="D469" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E469" s="5"/>
       <c r="F469" s="5" t="s">
@@ -19935,7 +19935,7 @@
         <v>390</v>
       </c>
       <c r="H469" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I469" s="5"/>
     </row>
@@ -19951,7 +19951,7 @@
         <v>348</v>
       </c>
       <c r="D470" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E470" s="5"/>
       <c r="F470" s="5" t="s">
@@ -19961,7 +19961,7 @@
         <v>271</v>
       </c>
       <c r="H470" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I470" s="5"/>
     </row>
@@ -19977,7 +19977,7 @@
         <v>57</v>
       </c>
       <c r="D471" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E471" s="5"/>
       <c r="F471" s="5" t="s">
@@ -19987,7 +19987,7 @@
         <v>392</v>
       </c>
       <c r="H471" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I471" s="5"/>
     </row>
@@ -20003,7 +20003,7 @@
         <v>346</v>
       </c>
       <c r="D472" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E472" s="5"/>
       <c r="F472" s="5" t="s">

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24700" windowHeight="14900" activeTab="3"/>
+    <workbookView windowWidth="22780" windowHeight="14900" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4195" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="604">
   <si>
     <t>name</t>
   </si>
@@ -2043,7 +2043,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2083,6 +2083,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2424,7 +2430,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2448,16 +2454,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2466,89 +2472,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2565,6 +2571,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
@@ -2987,7 +2994,7 @@
       </c>
     </row>
     <row r="4" ht="17" spans="1:9">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -3679,9 +3686,7 @@
       <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
@@ -3697,7 +3702,9 @@
       <c r="E21" s="6">
         <v>0</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="10" t="s">
@@ -4026,7 +4033,7 @@
       <c r="H2" s="6">
         <v>0</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4051,7 +4058,7 @@
       <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4076,7 +4083,7 @@
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4101,7 +4108,7 @@
       <c r="H5" s="6">
         <v>0</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4126,7 +4133,7 @@
       <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4151,7 +4158,7 @@
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4176,7 +4183,7 @@
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4201,7 +4208,7 @@
       <c r="H9" s="6">
         <v>0</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4226,7 +4233,7 @@
       <c r="H10" s="6">
         <v>0</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4251,7 +4258,7 @@
       <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4276,7 +4283,7 @@
       <c r="H12" s="6">
         <v>0</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4301,7 +4308,7 @@
       <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4326,7 +4333,7 @@
       <c r="H14" s="6">
         <v>0</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4353,7 +4360,7 @@
       <c r="H15" s="10">
         <v>0</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="18" t="s">
         <v>146</v>
       </c>
       <c r="J15" s="10"/>
@@ -4381,7 +4388,7 @@
       <c r="H16" s="10">
         <v>0</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="18" t="s">
         <v>148</v>
       </c>
       <c r="J16" s="10"/>
@@ -4409,7 +4416,7 @@
       <c r="H17" s="10">
         <v>0</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="18" t="s">
         <v>150</v>
       </c>
       <c r="J17" s="10"/>
@@ -4437,7 +4444,7 @@
       <c r="H18" s="10">
         <v>0</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="18" t="s">
         <v>152</v>
       </c>
       <c r="J18" s="10"/>
@@ -4465,7 +4472,7 @@
       <c r="H19" s="10">
         <v>0</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="18" t="s">
         <v>155</v>
       </c>
       <c r="J19" s="10"/>
@@ -4493,7 +4500,7 @@
       <c r="H20" s="10">
         <v>0</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="18" t="s">
         <v>157</v>
       </c>
       <c r="J20" s="10"/>
@@ -4521,7 +4528,7 @@
       <c r="H21" s="10">
         <v>0</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="18" t="s">
         <v>160</v>
       </c>
       <c r="J21" s="10">
@@ -4551,7 +4558,7 @@
       <c r="H22" s="6">
         <v>3</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4578,7 +4585,7 @@
       <c r="H23" s="6">
         <v>3</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4605,7 +4612,7 @@
       <c r="H24" s="6">
         <v>3</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4632,7 +4639,7 @@
       <c r="H25" s="6">
         <v>3</v>
       </c>
-      <c r="I25" s="16" t="s">
+      <c r="I25" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4653,13 +4660,13 @@
         <v>166</v>
       </c>
       <c r="F26" s="6"/>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H26" s="6">
         <v>3</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I26" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4686,7 +4693,7 @@
       <c r="H27" s="6">
         <v>3</v>
       </c>
-      <c r="I27" s="16" t="s">
+      <c r="I27" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4713,7 +4720,7 @@
       <c r="H28" s="6">
         <v>3</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I28" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4734,13 +4741,13 @@
         <v>170</v>
       </c>
       <c r="F29" s="6"/>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H29" s="6">
         <v>3</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4761,13 +4768,13 @@
         <v>170</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H30" s="6">
         <v>3</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4788,13 +4795,13 @@
         <v>170</v>
       </c>
       <c r="F31" s="6"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="17" t="s">
         <v>174</v>
       </c>
       <c r="H31" s="6">
         <v>3</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4815,13 +4822,13 @@
         <v>175</v>
       </c>
       <c r="F32" s="6"/>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="17" t="s">
         <v>176</v>
       </c>
       <c r="H32" s="6">
         <v>3</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4842,13 +4849,13 @@
         <v>175</v>
       </c>
       <c r="F33" s="6"/>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="19" t="s">
         <v>177</v>
       </c>
       <c r="H33" s="6">
         <v>3</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4869,13 +4876,13 @@
         <v>175</v>
       </c>
       <c r="F34" s="6"/>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="17" t="s">
         <v>178</v>
       </c>
       <c r="H34" s="6">
         <v>3</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4896,13 +4903,13 @@
         <v>179</v>
       </c>
       <c r="F35" s="6"/>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="17" t="s">
         <v>180</v>
       </c>
       <c r="H35" s="6">
         <v>3</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4931,7 +4938,7 @@
       <c r="H36" s="10">
         <v>3</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="I36" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J36" s="10"/>
@@ -4961,7 +4968,7 @@
       <c r="H37" s="10">
         <v>3</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J37" s="10"/>
@@ -4991,7 +4998,7 @@
       <c r="H38" s="10">
         <v>3</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J38" s="10"/>
@@ -5021,7 +5028,7 @@
       <c r="H39" s="10">
         <v>3</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J39" s="10"/>
@@ -5051,7 +5058,7 @@
       <c r="H40" s="10">
         <v>3</v>
       </c>
-      <c r="I40" s="19" t="s">
+      <c r="I40" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J40" s="10"/>
@@ -5081,7 +5088,7 @@
       <c r="H41" s="10">
         <v>3</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J41" s="10"/>
@@ -5111,7 +5118,7 @@
       <c r="H42" s="10">
         <v>3</v>
       </c>
-      <c r="I42" s="19" t="s">
+      <c r="I42" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J42" s="10"/>
@@ -5141,7 +5148,7 @@
       <c r="H43" s="10">
         <v>5</v>
       </c>
-      <c r="I43" s="19" t="s">
+      <c r="I43" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J43" s="10">
@@ -5173,7 +5180,7 @@
       <c r="H44" s="10">
         <v>3</v>
       </c>
-      <c r="I44" s="19" t="s">
+      <c r="I44" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J44" s="10"/>
@@ -5203,7 +5210,7 @@
       <c r="H45" s="10">
         <v>3</v>
       </c>
-      <c r="I45" s="19" t="s">
+      <c r="I45" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J45" s="10"/>
@@ -5233,7 +5240,7 @@
       <c r="H46" s="10">
         <v>3</v>
       </c>
-      <c r="I46" s="19" t="s">
+      <c r="I46" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J46" s="10"/>
@@ -5263,7 +5270,7 @@
       <c r="H47" s="10">
         <v>3</v>
       </c>
-      <c r="I47" s="19" t="s">
+      <c r="I47" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J47" s="10"/>
@@ -5293,7 +5300,7 @@
       <c r="H48" s="10">
         <v>3</v>
       </c>
-      <c r="I48" s="19" t="s">
+      <c r="I48" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J48" s="10"/>
@@ -5323,7 +5330,7 @@
       <c r="H49" s="10">
         <v>3</v>
       </c>
-      <c r="I49" s="19" t="s">
+      <c r="I49" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J49" s="10"/>
@@ -5351,7 +5358,7 @@
       <c r="H50" s="6">
         <v>1</v>
       </c>
-      <c r="I50" s="16" t="s">
+      <c r="I50" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5378,7 +5385,7 @@
       <c r="H51" s="6">
         <v>1</v>
       </c>
-      <c r="I51" s="16" t="s">
+      <c r="I51" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5405,7 +5412,7 @@
       <c r="H52" s="6">
         <v>1</v>
       </c>
-      <c r="I52" s="16" t="s">
+      <c r="I52" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5432,7 +5439,7 @@
       <c r="H53" s="6">
         <v>3</v>
       </c>
-      <c r="I53" s="16" t="s">
+      <c r="I53" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5453,13 +5460,13 @@
         <v>166</v>
       </c>
       <c r="F54" s="6"/>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H54" s="6">
         <v>1</v>
       </c>
-      <c r="I54" s="16" t="s">
+      <c r="I54" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5486,7 +5493,7 @@
       <c r="H55" s="6">
         <v>3</v>
       </c>
-      <c r="I55" s="16" t="s">
+      <c r="I55" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5507,13 +5514,13 @@
         <v>170</v>
       </c>
       <c r="F56" s="6"/>
-      <c r="G56" s="18" t="s">
+      <c r="G56" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H56" s="6">
         <v>3</v>
       </c>
-      <c r="I56" s="16" t="s">
+      <c r="I56" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5534,13 +5541,13 @@
         <v>170</v>
       </c>
       <c r="F57" s="6"/>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H57" s="6">
         <v>3</v>
       </c>
-      <c r="I57" s="16" t="s">
+      <c r="I57" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5561,13 +5568,13 @@
         <v>175</v>
       </c>
       <c r="F58" s="6"/>
-      <c r="G58" s="16" t="s">
+      <c r="G58" s="17" t="s">
         <v>177</v>
       </c>
       <c r="H58" s="6">
         <v>3</v>
       </c>
-      <c r="I58" s="16" t="s">
+      <c r="I58" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5594,7 +5601,7 @@
       <c r="H59" s="10">
         <v>5</v>
       </c>
-      <c r="I59" s="19" t="s">
+      <c r="I59" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J59" s="10"/>
@@ -5622,7 +5629,7 @@
       <c r="H60" s="10">
         <v>5</v>
       </c>
-      <c r="I60" s="19" t="s">
+      <c r="I60" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J60" s="10"/>
@@ -5650,7 +5657,7 @@
       <c r="H61" s="10">
         <v>5</v>
       </c>
-      <c r="I61" s="19" t="s">
+      <c r="I61" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J61" s="10"/>
@@ -5678,7 +5685,7 @@
       <c r="H62" s="10">
         <v>5</v>
       </c>
-      <c r="I62" s="19" t="s">
+      <c r="I62" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J62" s="10"/>
@@ -5706,7 +5713,7 @@
       <c r="H63" s="10">
         <v>5</v>
       </c>
-      <c r="I63" s="19" t="s">
+      <c r="I63" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J63" s="10"/>
@@ -5734,7 +5741,7 @@
       <c r="H64" s="10">
         <v>5</v>
       </c>
-      <c r="I64" s="19" t="s">
+      <c r="I64" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J64" s="10"/>
@@ -5762,7 +5769,7 @@
       <c r="H65" s="10">
         <v>5</v>
       </c>
-      <c r="I65" s="19" t="s">
+      <c r="I65" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J65" s="10">
@@ -5792,7 +5799,7 @@
       <c r="H66" s="6">
         <v>1</v>
       </c>
-      <c r="I66" s="16" t="s">
+      <c r="I66" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5819,7 +5826,7 @@
       <c r="H67" s="6">
         <v>1</v>
       </c>
-      <c r="I67" s="16" t="s">
+      <c r="I67" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5846,7 +5853,7 @@
       <c r="H68" s="6">
         <v>1</v>
       </c>
-      <c r="I68" s="16" t="s">
+      <c r="I68" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5873,7 +5880,7 @@
       <c r="H69" s="6">
         <v>3</v>
       </c>
-      <c r="I69" s="16" t="s">
+      <c r="I69" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5894,13 +5901,13 @@
         <v>166</v>
       </c>
       <c r="F70" s="6"/>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H70" s="6">
         <v>1</v>
       </c>
-      <c r="I70" s="16" t="s">
+      <c r="I70" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5927,7 +5934,7 @@
       <c r="H71" s="6">
         <v>3</v>
       </c>
-      <c r="I71" s="16" t="s">
+      <c r="I71" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5948,13 +5955,13 @@
         <v>170</v>
       </c>
       <c r="F72" s="6"/>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H72" s="6">
         <v>3</v>
       </c>
-      <c r="I72" s="16" t="s">
+      <c r="I72" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5975,13 +5982,13 @@
         <v>170</v>
       </c>
       <c r="F73" s="6"/>
-      <c r="G73" s="16" t="s">
+      <c r="G73" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H73" s="6">
         <v>3</v>
       </c>
-      <c r="I73" s="16" t="s">
+      <c r="I73" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6002,13 +6009,13 @@
         <v>175</v>
       </c>
       <c r="F74" s="6"/>
-      <c r="G74" s="16" t="s">
+      <c r="G74" s="17" t="s">
         <v>177</v>
       </c>
       <c r="H74" s="6">
         <v>3</v>
       </c>
-      <c r="I74" s="16" t="s">
+      <c r="I74" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6035,7 +6042,7 @@
       <c r="H75" s="10">
         <v>1</v>
       </c>
-      <c r="I75" s="19" t="s">
+      <c r="I75" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J75" s="10"/>
@@ -6063,7 +6070,7 @@
       <c r="H76" s="10">
         <v>1</v>
       </c>
-      <c r="I76" s="19" t="s">
+      <c r="I76" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J76" s="10"/>
@@ -6091,7 +6098,7 @@
       <c r="H77" s="10">
         <v>1</v>
       </c>
-      <c r="I77" s="19" t="s">
+      <c r="I77" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J77" s="10"/>
@@ -6119,7 +6126,7 @@
       <c r="H78" s="10">
         <v>3</v>
       </c>
-      <c r="I78" s="19" t="s">
+      <c r="I78" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J78" s="10"/>
@@ -6141,13 +6148,13 @@
         <v>166</v>
       </c>
       <c r="F79" s="10"/>
-      <c r="G79" s="17" t="s">
+      <c r="G79" s="18" t="s">
         <v>168</v>
       </c>
       <c r="H79" s="10">
         <v>1</v>
       </c>
-      <c r="I79" s="19" t="s">
+      <c r="I79" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J79" s="10"/>
@@ -6175,7 +6182,7 @@
       <c r="H80" s="10">
         <v>3</v>
       </c>
-      <c r="I80" s="19" t="s">
+      <c r="I80" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J80" s="10"/>
@@ -6197,13 +6204,13 @@
         <v>170</v>
       </c>
       <c r="F81" s="10"/>
-      <c r="G81" s="17" t="s">
+      <c r="G81" s="18" t="s">
         <v>172</v>
       </c>
       <c r="H81" s="10">
         <v>3</v>
       </c>
-      <c r="I81" s="19" t="s">
+      <c r="I81" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J81" s="10"/>
@@ -6225,13 +6232,13 @@
         <v>170</v>
       </c>
       <c r="F82" s="10"/>
-      <c r="G82" s="19" t="s">
+      <c r="G82" s="20" t="s">
         <v>173</v>
       </c>
       <c r="H82" s="10">
         <v>3</v>
       </c>
-      <c r="I82" s="19" t="s">
+      <c r="I82" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J82" s="10"/>
@@ -6253,13 +6260,13 @@
         <v>175</v>
       </c>
       <c r="F83" s="10"/>
-      <c r="G83" s="19" t="s">
+      <c r="G83" s="20" t="s">
         <v>177</v>
       </c>
       <c r="H83" s="10">
         <v>3</v>
       </c>
-      <c r="I83" s="19" t="s">
+      <c r="I83" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J83" s="10"/>
@@ -6287,7 +6294,7 @@
       <c r="H84" s="6">
         <v>1</v>
       </c>
-      <c r="I84" s="16" t="s">
+      <c r="I84" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6314,7 +6321,7 @@
       <c r="H85" s="6">
         <v>1</v>
       </c>
-      <c r="I85" s="16" t="s">
+      <c r="I85" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6341,7 +6348,7 @@
       <c r="H86" s="6">
         <v>1</v>
       </c>
-      <c r="I86" s="16" t="s">
+      <c r="I86" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6368,7 +6375,7 @@
       <c r="H87" s="6">
         <v>3</v>
       </c>
-      <c r="I87" s="16" t="s">
+      <c r="I87" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6389,13 +6396,13 @@
         <v>166</v>
       </c>
       <c r="F88" s="6"/>
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H88" s="6">
         <v>1</v>
       </c>
-      <c r="I88" s="16" t="s">
+      <c r="I88" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6422,7 +6429,7 @@
       <c r="H89" s="6">
         <v>3</v>
       </c>
-      <c r="I89" s="16" t="s">
+      <c r="I89" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6443,13 +6450,13 @@
         <v>170</v>
       </c>
       <c r="F90" s="6"/>
-      <c r="G90" s="18" t="s">
+      <c r="G90" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H90" s="6">
         <v>3</v>
       </c>
-      <c r="I90" s="16" t="s">
+      <c r="I90" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6470,13 +6477,13 @@
         <v>170</v>
       </c>
       <c r="F91" s="6"/>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H91" s="6">
         <v>3</v>
       </c>
-      <c r="I91" s="16" t="s">
+      <c r="I91" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6497,13 +6504,13 @@
         <v>175</v>
       </c>
       <c r="F92" s="6"/>
-      <c r="G92" s="16" t="s">
+      <c r="G92" s="17" t="s">
         <v>177</v>
       </c>
       <c r="H92" s="6">
         <v>3</v>
       </c>
-      <c r="I92" s="16" t="s">
+      <c r="I92" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6530,7 +6537,7 @@
       <c r="H93" s="10">
         <v>3</v>
       </c>
-      <c r="I93" s="19" t="s">
+      <c r="I93" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J93" s="10"/>
@@ -6558,7 +6565,7 @@
       <c r="H94" s="10">
         <v>3</v>
       </c>
-      <c r="I94" s="19" t="s">
+      <c r="I94" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J94" s="10"/>
@@ -6586,7 +6593,7 @@
       <c r="H95" s="10">
         <v>3</v>
       </c>
-      <c r="I95" s="19" t="s">
+      <c r="I95" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J95" s="10"/>
@@ -6614,7 +6621,7 @@
       <c r="H96" s="10">
         <v>3</v>
       </c>
-      <c r="I96" s="19" t="s">
+      <c r="I96" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J96" s="10"/>
@@ -6642,7 +6649,7 @@
       <c r="H97" s="10">
         <v>3</v>
       </c>
-      <c r="I97" s="19" t="s">
+      <c r="I97" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J97" s="10"/>
@@ -6670,7 +6677,7 @@
       <c r="H98" s="10">
         <v>3</v>
       </c>
-      <c r="I98" s="19" t="s">
+      <c r="I98" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J98" s="10"/>
@@ -6698,7 +6705,7 @@
       <c r="H99" s="10">
         <v>5</v>
       </c>
-      <c r="I99" s="19" t="s">
+      <c r="I99" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J99" s="10">
@@ -6730,7 +6737,7 @@
       <c r="H100" s="6">
         <v>5</v>
       </c>
-      <c r="I100" s="16" t="s">
+      <c r="I100" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6759,7 +6766,7 @@
       <c r="H101" s="6">
         <v>5</v>
       </c>
-      <c r="I101" s="16" t="s">
+      <c r="I101" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6788,7 +6795,7 @@
       <c r="H102" s="6">
         <v>5</v>
       </c>
-      <c r="I102" s="16" t="s">
+      <c r="I102" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6817,7 +6824,7 @@
       <c r="H103" s="6">
         <v>5</v>
       </c>
-      <c r="I103" s="16" t="s">
+      <c r="I103" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6846,7 +6853,7 @@
       <c r="H104" s="6">
         <v>5</v>
       </c>
-      <c r="I104" s="16" t="s">
+      <c r="I104" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6875,7 +6882,7 @@
       <c r="H105" s="10">
         <v>5</v>
       </c>
-      <c r="I105" s="19" t="s">
+      <c r="I105" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J105" s="10"/>
@@ -6905,7 +6912,7 @@
       <c r="H106" s="10">
         <v>5</v>
       </c>
-      <c r="I106" s="19" t="s">
+      <c r="I106" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J106" s="10"/>
@@ -6935,7 +6942,7 @@
       <c r="H107" s="10">
         <v>5</v>
       </c>
-      <c r="I107" s="19" t="s">
+      <c r="I107" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J107" s="10"/>
@@ -6965,7 +6972,7 @@
       <c r="H108" s="10">
         <v>5</v>
       </c>
-      <c r="I108" s="19" t="s">
+      <c r="I108" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J108" s="10"/>
@@ -6995,7 +7002,7 @@
       <c r="H109" s="10">
         <v>5</v>
       </c>
-      <c r="I109" s="19" t="s">
+      <c r="I109" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J109" s="10"/>
@@ -7023,7 +7030,7 @@
       <c r="H110" s="6">
         <v>5</v>
       </c>
-      <c r="I110" s="16" t="s">
+      <c r="I110" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7050,7 +7057,7 @@
       <c r="H111" s="6">
         <v>5</v>
       </c>
-      <c r="I111" s="16" t="s">
+      <c r="I111" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7077,7 +7084,7 @@
       <c r="H112" s="6">
         <v>5</v>
       </c>
-      <c r="I112" s="16" t="s">
+      <c r="I112" s="17" t="s">
         <v>131</v>
       </c>
       <c r="J112" s="6">
@@ -7105,7 +7112,7 @@
       <c r="H113" s="10">
         <v>0</v>
       </c>
-      <c r="I113" s="19" t="s">
+      <c r="I113" s="20" t="s">
         <v>192</v>
       </c>
       <c r="J113" s="10"/>
@@ -7131,7 +7138,7 @@
       <c r="H114" s="10">
         <v>0</v>
       </c>
-      <c r="I114" s="19" t="s">
+      <c r="I114" s="20" t="s">
         <v>193</v>
       </c>
       <c r="J114" s="10"/>
@@ -7157,7 +7164,7 @@
       <c r="H115" s="10">
         <v>0</v>
       </c>
-      <c r="I115" s="19" t="s">
+      <c r="I115" s="20" t="s">
         <v>194</v>
       </c>
       <c r="J115" s="10"/>
@@ -7183,7 +7190,7 @@
       <c r="H116" s="10">
         <v>0</v>
       </c>
-      <c r="I116" s="19" t="s">
+      <c r="I116" s="20" t="s">
         <v>195</v>
       </c>
       <c r="J116" s="10"/>
@@ -7209,7 +7216,7 @@
       <c r="H117" s="10">
         <v>0</v>
       </c>
-      <c r="I117" s="19" t="s">
+      <c r="I117" s="20" t="s">
         <v>196</v>
       </c>
       <c r="J117" s="10"/>
@@ -7235,7 +7242,7 @@
       <c r="H118" s="10">
         <v>0</v>
       </c>
-      <c r="I118" s="19" t="s">
+      <c r="I118" s="20" t="s">
         <v>197</v>
       </c>
       <c r="J118" s="10"/>
@@ -7261,7 +7268,7 @@
       <c r="H119" s="10">
         <v>0</v>
       </c>
-      <c r="I119" s="19" t="s">
+      <c r="I119" s="20" t="s">
         <v>198</v>
       </c>
       <c r="J119" s="10"/>
@@ -7287,7 +7294,7 @@
       <c r="H120" s="10">
         <v>0</v>
       </c>
-      <c r="I120" s="19" t="s">
+      <c r="I120" s="20" t="s">
         <v>199</v>
       </c>
       <c r="J120" s="10"/>
@@ -7313,7 +7320,7 @@
       <c r="H121" s="10">
         <v>0</v>
       </c>
-      <c r="I121" s="19" t="s">
+      <c r="I121" s="20" t="s">
         <v>200</v>
       </c>
       <c r="J121" s="10"/>
@@ -7339,7 +7346,7 @@
       <c r="H122" s="10">
         <v>0</v>
       </c>
-      <c r="I122" s="19" t="s">
+      <c r="I122" s="20" t="s">
         <v>201</v>
       </c>
       <c r="J122" s="10"/>
@@ -7365,7 +7372,7 @@
       <c r="H123" s="10">
         <v>0</v>
       </c>
-      <c r="I123" s="19" t="s">
+      <c r="I123" s="20" t="s">
         <v>202</v>
       </c>
       <c r="J123" s="10"/>
@@ -7391,7 +7398,7 @@
       <c r="H124" s="10">
         <v>0</v>
       </c>
-      <c r="I124" s="19" t="s">
+      <c r="I124" s="20" t="s">
         <v>203</v>
       </c>
       <c r="J124" s="10"/>
@@ -7417,7 +7424,7 @@
       <c r="H125" s="10">
         <v>0</v>
       </c>
-      <c r="I125" s="19" t="s">
+      <c r="I125" s="20" t="s">
         <v>204</v>
       </c>
       <c r="J125" s="10"/>
@@ -7443,7 +7450,7 @@
       <c r="H126" s="10">
         <v>0</v>
       </c>
-      <c r="I126" s="19" t="s">
+      <c r="I126" s="20" t="s">
         <v>206</v>
       </c>
       <c r="J126" s="10"/>
@@ -7469,7 +7476,7 @@
       <c r="H127" s="10">
         <v>0</v>
       </c>
-      <c r="I127" s="19" t="s">
+      <c r="I127" s="20" t="s">
         <v>208</v>
       </c>
       <c r="J127" s="10"/>
@@ -7495,7 +7502,7 @@
       <c r="H128" s="10">
         <v>0</v>
       </c>
-      <c r="I128" s="19" t="s">
+      <c r="I128" s="20" t="s">
         <v>210</v>
       </c>
       <c r="J128" s="10"/>
@@ -7521,7 +7528,7 @@
       <c r="H129" s="10">
         <v>0</v>
       </c>
-      <c r="I129" s="19" t="s">
+      <c r="I129" s="20" t="s">
         <v>212</v>
       </c>
       <c r="J129" s="10"/>
@@ -7547,7 +7554,7 @@
       <c r="H130" s="10">
         <v>0</v>
       </c>
-      <c r="I130" s="19" t="s">
+      <c r="I130" s="20" t="s">
         <v>214</v>
       </c>
       <c r="J130" s="10"/>
@@ -7573,7 +7580,7 @@
       <c r="H131" s="10">
         <v>0</v>
       </c>
-      <c r="I131" s="19" t="s">
+      <c r="I131" s="20" t="s">
         <v>216</v>
       </c>
       <c r="J131" s="10"/>
@@ -7599,7 +7606,7 @@
       <c r="H132" s="10">
         <v>0</v>
       </c>
-      <c r="I132" s="19" t="s">
+      <c r="I132" s="20" t="s">
         <v>218</v>
       </c>
       <c r="J132" s="10"/>
@@ -7625,7 +7632,7 @@
       <c r="H133" s="10">
         <v>0</v>
       </c>
-      <c r="I133" s="19" t="s">
+      <c r="I133" s="20" t="s">
         <v>220</v>
       </c>
       <c r="J133" s="10"/>
@@ -7651,7 +7658,7 @@
       <c r="H134" s="10">
         <v>0</v>
       </c>
-      <c r="I134" s="19" t="s">
+      <c r="I134" s="20" t="s">
         <v>222</v>
       </c>
       <c r="J134" s="10"/>
@@ -7679,7 +7686,7 @@
       <c r="H135" s="6">
         <v>0</v>
       </c>
-      <c r="I135" s="16" t="s">
+      <c r="I135" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7706,7 +7713,7 @@
       <c r="H136" s="6">
         <v>0</v>
       </c>
-      <c r="I136" s="16" t="s">
+      <c r="I136" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7733,7 +7740,7 @@
       <c r="H137" s="6">
         <v>0</v>
       </c>
-      <c r="I137" s="16" t="s">
+      <c r="I137" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7760,7 +7767,7 @@
       <c r="H138" s="6">
         <v>0</v>
       </c>
-      <c r="I138" s="16" t="s">
+      <c r="I138" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7787,7 +7794,7 @@
       <c r="H139" s="6">
         <v>0</v>
       </c>
-      <c r="I139" s="16" t="s">
+      <c r="I139" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7814,7 +7821,7 @@
       <c r="H140" s="6">
         <v>0</v>
       </c>
-      <c r="I140" s="16" t="s">
+      <c r="I140" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7841,7 +7848,7 @@
       <c r="H141" s="6">
         <v>0</v>
       </c>
-      <c r="I141" s="16" t="s">
+      <c r="I141" s="17" t="s">
         <v>131</v>
       </c>
       <c r="J141" s="6">
@@ -7873,7 +7880,7 @@
       <c r="H142" s="10">
         <v>5</v>
       </c>
-      <c r="I142" s="19" t="s">
+      <c r="I142" s="20" t="s">
         <v>223</v>
       </c>
       <c r="J142" s="10"/>
@@ -7903,7 +7910,7 @@
       <c r="H143" s="10">
         <v>5</v>
       </c>
-      <c r="I143" s="19" t="s">
+      <c r="I143" s="20" t="s">
         <v>223</v>
       </c>
       <c r="J143" s="10"/>
@@ -7933,7 +7940,7 @@
       <c r="H144" s="10">
         <v>5</v>
       </c>
-      <c r="I144" s="19" t="s">
+      <c r="I144" s="20" t="s">
         <v>199</v>
       </c>
       <c r="J144" s="10"/>
@@ -7963,7 +7970,7 @@
       <c r="H145" s="10">
         <v>5</v>
       </c>
-      <c r="I145" s="19" t="s">
+      <c r="I145" s="20" t="s">
         <v>199</v>
       </c>
       <c r="J145" s="10"/>
@@ -7993,7 +8000,7 @@
       <c r="H146" s="10">
         <v>5</v>
       </c>
-      <c r="I146" s="19" t="s">
+      <c r="I146" s="20" t="s">
         <v>224</v>
       </c>
       <c r="J146" s="10"/>
@@ -8023,7 +8030,7 @@
       <c r="H147" s="10">
         <v>5</v>
       </c>
-      <c r="I147" s="19" t="s">
+      <c r="I147" s="20" t="s">
         <v>225</v>
       </c>
       <c r="J147" s="10"/>
@@ -8053,7 +8060,7 @@
       <c r="H148" s="10">
         <v>5</v>
       </c>
-      <c r="I148" s="19" t="s">
+      <c r="I148" s="20" t="s">
         <v>226</v>
       </c>
       <c r="J148" s="10"/>
@@ -8083,7 +8090,7 @@
       <c r="H149" s="10">
         <v>5</v>
       </c>
-      <c r="I149" s="19" t="s">
+      <c r="I149" s="20" t="s">
         <v>227</v>
       </c>
       <c r="J149" s="10">
@@ -8115,7 +8122,7 @@
       <c r="H150" s="10">
         <v>5</v>
       </c>
-      <c r="I150" s="19" t="s">
+      <c r="I150" s="20" t="s">
         <v>228</v>
       </c>
       <c r="J150" s="10"/>
@@ -8145,7 +8152,7 @@
       <c r="H151" s="10">
         <v>5</v>
       </c>
-      <c r="I151" s="19" t="s">
+      <c r="I151" s="20" t="s">
         <v>229</v>
       </c>
       <c r="J151" s="10"/>
@@ -8175,7 +8182,7 @@
       <c r="H152" s="10">
         <v>5</v>
       </c>
-      <c r="I152" s="19" t="s">
+      <c r="I152" s="20" t="s">
         <v>230</v>
       </c>
       <c r="J152" s="10"/>
@@ -8205,7 +8212,7 @@
       <c r="H153" s="10">
         <v>5</v>
       </c>
-      <c r="I153" s="19" t="s">
+      <c r="I153" s="20" t="s">
         <v>231</v>
       </c>
       <c r="J153" s="10"/>
@@ -8235,7 +8242,7 @@
       <c r="H154" s="10">
         <v>5</v>
       </c>
-      <c r="I154" s="19" t="s">
+      <c r="I154" s="20" t="s">
         <v>232</v>
       </c>
       <c r="J154" s="10"/>
@@ -8265,7 +8272,7 @@
       <c r="H155" s="10">
         <v>5</v>
       </c>
-      <c r="I155" s="19" t="s">
+      <c r="I155" s="20" t="s">
         <v>200</v>
       </c>
       <c r="J155" s="10"/>
@@ -8293,7 +8300,7 @@
       <c r="H156" s="6">
         <v>1</v>
       </c>
-      <c r="I156" s="16" t="s">
+      <c r="I156" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8320,7 +8327,7 @@
       <c r="H157" s="6">
         <v>1</v>
       </c>
-      <c r="I157" s="16" t="s">
+      <c r="I157" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8347,7 +8354,7 @@
       <c r="H158" s="6">
         <v>1</v>
       </c>
-      <c r="I158" s="16" t="s">
+      <c r="I158" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8374,7 +8381,7 @@
       <c r="H159" s="6">
         <v>3</v>
       </c>
-      <c r="I159" s="16" t="s">
+      <c r="I159" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8395,13 +8402,13 @@
         <v>166</v>
       </c>
       <c r="F160" s="6"/>
-      <c r="G160" s="18" t="s">
+      <c r="G160" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H160" s="6">
         <v>1</v>
       </c>
-      <c r="I160" s="16" t="s">
+      <c r="I160" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8428,7 +8435,7 @@
       <c r="H161" s="6">
         <v>3</v>
       </c>
-      <c r="I161" s="16" t="s">
+      <c r="I161" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8449,13 +8456,13 @@
         <v>170</v>
       </c>
       <c r="F162" s="6"/>
-      <c r="G162" s="18" t="s">
+      <c r="G162" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H162" s="6">
         <v>3</v>
       </c>
-      <c r="I162" s="16" t="s">
+      <c r="I162" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8476,13 +8483,13 @@
         <v>170</v>
       </c>
       <c r="F163" s="6"/>
-      <c r="G163" s="16" t="s">
+      <c r="G163" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H163" s="6">
         <v>3</v>
       </c>
-      <c r="I163" s="16" t="s">
+      <c r="I163" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8503,13 +8510,13 @@
         <v>175</v>
       </c>
       <c r="F164" s="6"/>
-      <c r="G164" s="16" t="s">
+      <c r="G164" s="17" t="s">
         <v>177</v>
       </c>
       <c r="H164" s="6">
         <v>3</v>
       </c>
-      <c r="I164" s="16" t="s">
+      <c r="I164" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8536,7 +8543,7 @@
       <c r="H165" s="10">
         <v>1</v>
       </c>
-      <c r="I165" s="19" t="s">
+      <c r="I165" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J165" s="10"/>
@@ -8564,7 +8571,7 @@
       <c r="H166" s="10">
         <v>1</v>
       </c>
-      <c r="I166" s="19" t="s">
+      <c r="I166" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J166" s="10"/>
@@ -8592,7 +8599,7 @@
       <c r="H167" s="10">
         <v>1</v>
       </c>
-      <c r="I167" s="19" t="s">
+      <c r="I167" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J167" s="10"/>
@@ -8620,7 +8627,7 @@
       <c r="H168" s="10">
         <v>3</v>
       </c>
-      <c r="I168" s="19" t="s">
+      <c r="I168" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J168" s="10"/>
@@ -8642,13 +8649,13 @@
         <v>166</v>
       </c>
       <c r="F169" s="10"/>
-      <c r="G169" s="17" t="s">
+      <c r="G169" s="18" t="s">
         <v>168</v>
       </c>
       <c r="H169" s="10">
         <v>1</v>
       </c>
-      <c r="I169" s="19" t="s">
+      <c r="I169" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J169" s="10"/>
@@ -8676,7 +8683,7 @@
       <c r="H170" s="10">
         <v>3</v>
       </c>
-      <c r="I170" s="19" t="s">
+      <c r="I170" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J170" s="10"/>
@@ -8698,13 +8705,13 @@
         <v>170</v>
       </c>
       <c r="F171" s="10"/>
-      <c r="G171" s="17" t="s">
+      <c r="G171" s="18" t="s">
         <v>172</v>
       </c>
       <c r="H171" s="10">
         <v>3</v>
       </c>
-      <c r="I171" s="19" t="s">
+      <c r="I171" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J171" s="10"/>
@@ -8726,13 +8733,13 @@
         <v>170</v>
       </c>
       <c r="F172" s="10"/>
-      <c r="G172" s="19" t="s">
+      <c r="G172" s="20" t="s">
         <v>173</v>
       </c>
       <c r="H172" s="10">
         <v>3</v>
       </c>
-      <c r="I172" s="19" t="s">
+      <c r="I172" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J172" s="10"/>
@@ -8754,13 +8761,13 @@
         <v>175</v>
       </c>
       <c r="F173" s="10"/>
-      <c r="G173" s="19" t="s">
+      <c r="G173" s="20" t="s">
         <v>177</v>
       </c>
       <c r="H173" s="10">
         <v>3</v>
       </c>
-      <c r="I173" s="19" t="s">
+      <c r="I173" s="20" t="s">
         <v>131</v>
       </c>
       <c r="J173" s="10"/>
@@ -8788,7 +8795,7 @@
       <c r="H174" s="6">
         <v>3</v>
       </c>
-      <c r="I174" s="16" t="s">
+      <c r="I174" s="17" t="s">
         <v>233</v>
       </c>
     </row>
@@ -8815,7 +8822,7 @@
       <c r="H175" s="6">
         <v>3</v>
       </c>
-      <c r="I175" s="16" t="s">
+      <c r="I175" s="17" t="s">
         <v>234</v>
       </c>
     </row>
@@ -8842,7 +8849,7 @@
       <c r="H176" s="6">
         <v>3</v>
       </c>
-      <c r="I176" s="16" t="s">
+      <c r="I176" s="17" t="s">
         <v>234</v>
       </c>
     </row>
@@ -8869,7 +8876,7 @@
       <c r="H177" s="6">
         <v>3</v>
       </c>
-      <c r="I177" s="16" t="s">
+      <c r="I177" s="17" t="s">
         <v>200</v>
       </c>
     </row>
@@ -8890,13 +8897,13 @@
         <v>166</v>
       </c>
       <c r="F178" s="6"/>
-      <c r="G178" s="18" t="s">
+      <c r="G178" s="19" t="s">
         <v>168</v>
       </c>
       <c r="H178" s="6">
         <v>3</v>
       </c>
-      <c r="I178" s="16" t="s">
+      <c r="I178" s="17" t="s">
         <v>200</v>
       </c>
     </row>
@@ -8923,7 +8930,7 @@
       <c r="H179" s="6">
         <v>3</v>
       </c>
-      <c r="I179" s="16" t="s">
+      <c r="I179" s="17" t="s">
         <v>200</v>
       </c>
     </row>
@@ -8944,13 +8951,13 @@
         <v>170</v>
       </c>
       <c r="F180" s="6"/>
-      <c r="G180" s="18" t="s">
+      <c r="G180" s="19" t="s">
         <v>172</v>
       </c>
       <c r="H180" s="6">
         <v>3</v>
       </c>
-      <c r="I180" s="16" t="s">
+      <c r="I180" s="17" t="s">
         <v>227</v>
       </c>
     </row>
@@ -8971,13 +8978,13 @@
         <v>170</v>
       </c>
       <c r="F181" s="6"/>
-      <c r="G181" s="16" t="s">
+      <c r="G181" s="17" t="s">
         <v>173</v>
       </c>
       <c r="H181" s="6">
         <v>3</v>
       </c>
-      <c r="I181" s="16" t="s">
+      <c r="I181" s="17" t="s">
         <v>227</v>
       </c>
     </row>
@@ -8998,13 +9005,13 @@
         <v>175</v>
       </c>
       <c r="F182" s="6"/>
-      <c r="G182" s="16" t="s">
+      <c r="G182" s="17" t="s">
         <v>177</v>
       </c>
       <c r="H182" s="6">
         <v>3</v>
       </c>
-      <c r="I182" s="16" t="s">
+      <c r="I182" s="17" t="s">
         <v>235</v>
       </c>
     </row>
@@ -9031,7 +9038,7 @@
       <c r="H183" s="10">
         <v>3</v>
       </c>
-      <c r="I183" s="19" t="s">
+      <c r="I183" s="20" t="s">
         <v>236</v>
       </c>
       <c r="J183" s="10"/>
@@ -9059,7 +9066,7 @@
       <c r="H184" s="10">
         <v>3</v>
       </c>
-      <c r="I184" s="19" t="s">
+      <c r="I184" s="20" t="s">
         <v>237</v>
       </c>
       <c r="J184" s="10"/>
@@ -9087,7 +9094,7 @@
       <c r="H185" s="10">
         <v>3</v>
       </c>
-      <c r="I185" s="19" t="s">
+      <c r="I185" s="20" t="s">
         <v>237</v>
       </c>
       <c r="J185" s="10"/>
@@ -9115,7 +9122,7 @@
       <c r="H186" s="10">
         <v>3</v>
       </c>
-      <c r="I186" s="19" t="s">
+      <c r="I186" s="20" t="s">
         <v>201</v>
       </c>
       <c r="J186" s="10"/>
@@ -9143,7 +9150,7 @@
       <c r="H187" s="10">
         <v>3</v>
       </c>
-      <c r="I187" s="19" t="s">
+      <c r="I187" s="20" t="s">
         <v>201</v>
       </c>
       <c r="J187" s="10"/>
@@ -9171,7 +9178,7 @@
       <c r="H188" s="10">
         <v>3</v>
       </c>
-      <c r="I188" s="19" t="s">
+      <c r="I188" s="20" t="s">
         <v>238</v>
       </c>
       <c r="J188" s="10"/>
@@ -9199,7 +9206,7 @@
       <c r="H189" s="10">
         <v>5</v>
       </c>
-      <c r="I189" s="19" t="s">
+      <c r="I189" s="20" t="s">
         <v>238</v>
       </c>
       <c r="J189" s="10">
@@ -9223,7 +9230,7 @@
       <c r="F190" s="12"/>
       <c r="G190" s="12"/>
       <c r="H190" s="12"/>
-      <c r="I190" s="16" t="s">
+      <c r="I190" s="17" t="s">
         <v>234</v>
       </c>
       <c r="J190" s="12"/>
@@ -9245,7 +9252,7 @@
       <c r="F191" s="12"/>
       <c r="G191" s="12"/>
       <c r="H191" s="12"/>
-      <c r="I191" s="16" t="s">
+      <c r="I191" s="17" t="s">
         <v>237</v>
       </c>
     </row>
@@ -9266,7 +9273,7 @@
       <c r="F192" s="12"/>
       <c r="G192" s="12"/>
       <c r="H192" s="12"/>
-      <c r="I192" s="16" t="s">
+      <c r="I192" s="17" t="s">
         <v>239</v>
       </c>
     </row>
@@ -9287,7 +9294,7 @@
       <c r="F193" s="12"/>
       <c r="G193" s="12"/>
       <c r="H193" s="12"/>
-      <c r="I193" s="16" t="s">
+      <c r="I193" s="17" t="s">
         <v>200</v>
       </c>
     </row>
@@ -9308,7 +9315,7 @@
       <c r="F194" s="12"/>
       <c r="G194" s="12"/>
       <c r="H194" s="12"/>
-      <c r="I194" s="16" t="s">
+      <c r="I194" s="17" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9329,7 +9336,7 @@
       <c r="F195" s="12"/>
       <c r="G195" s="12"/>
       <c r="H195" s="12"/>
-      <c r="I195" s="16" t="s">
+      <c r="I195" s="17" t="s">
         <v>237</v>
       </c>
     </row>
@@ -9350,7 +9357,7 @@
       <c r="F196" s="12"/>
       <c r="G196" s="12"/>
       <c r="H196" s="12"/>
-      <c r="I196" s="16" t="s">
+      <c r="I196" s="17" t="s">
         <v>239</v>
       </c>
     </row>
@@ -9371,7 +9378,7 @@
       <c r="F197" s="12"/>
       <c r="G197" s="12"/>
       <c r="H197" s="12"/>
-      <c r="I197" s="16" t="s">
+      <c r="I197" s="17" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9392,7 +9399,7 @@
       <c r="F198" s="12"/>
       <c r="G198" s="12"/>
       <c r="H198" s="12"/>
-      <c r="I198" s="16" t="s">
+      <c r="I198" s="17" t="s">
         <v>201</v>
       </c>
     </row>
@@ -9413,7 +9420,7 @@
       <c r="F199" s="12"/>
       <c r="G199" s="12"/>
       <c r="H199" s="12"/>
-      <c r="I199" s="16" t="s">
+      <c r="I199" s="17" t="s">
         <v>239</v>
       </c>
     </row>
@@ -9434,7 +9441,7 @@
       <c r="F200" s="12"/>
       <c r="G200" s="12"/>
       <c r="H200" s="12"/>
-      <c r="I200" s="16" t="s">
+      <c r="I200" s="17" t="s">
         <v>200</v>
       </c>
     </row>
@@ -9455,7 +9462,7 @@
       <c r="F201" s="12"/>
       <c r="G201" s="12"/>
       <c r="H201" s="12"/>
-      <c r="I201" s="16" t="s">
+      <c r="I201" s="17" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9476,7 +9483,7 @@
       <c r="F202" s="12"/>
       <c r="G202" s="12"/>
       <c r="H202" s="12"/>
-      <c r="I202" s="16" t="s">
+      <c r="I202" s="17" t="s">
         <v>201</v>
       </c>
     </row>
@@ -9497,7 +9504,7 @@
       <c r="F203" s="12"/>
       <c r="G203" s="12"/>
       <c r="H203" s="12"/>
-      <c r="I203" s="16" t="s">
+      <c r="I203" s="17" t="s">
         <v>240</v>
       </c>
     </row>
@@ -9518,7 +9525,7 @@
       <c r="F204" s="12"/>
       <c r="G204" s="12"/>
       <c r="H204" s="12"/>
-      <c r="I204" s="16" t="s">
+      <c r="I204" s="17" t="s">
         <v>235</v>
       </c>
     </row>
@@ -9539,7 +9546,7 @@
       <c r="F205" s="12"/>
       <c r="G205" s="12"/>
       <c r="H205" s="12"/>
-      <c r="I205" s="16" t="s">
+      <c r="I205" s="17" t="s">
         <v>238</v>
       </c>
     </row>
@@ -9560,7 +9567,7 @@
       <c r="F206" s="12"/>
       <c r="G206" s="12"/>
       <c r="H206" s="12"/>
-      <c r="I206" s="16" t="s">
+      <c r="I206" s="17" t="s">
         <v>240</v>
       </c>
     </row>
@@ -9581,7 +9588,7 @@
       <c r="F207" s="12"/>
       <c r="G207" s="12"/>
       <c r="H207" s="12"/>
-      <c r="I207" s="16" t="s">
+      <c r="I207" s="17" t="s">
         <v>235</v>
       </c>
     </row>
@@ -9602,7 +9609,7 @@
       <c r="F208" s="12"/>
       <c r="G208" s="12"/>
       <c r="H208" s="12"/>
-      <c r="I208" s="16" t="s">
+      <c r="I208" s="17" t="s">
         <v>238</v>
       </c>
     </row>
@@ -9623,7 +9630,7 @@
       <c r="F209" s="12"/>
       <c r="G209" s="12"/>
       <c r="H209" s="12"/>
-      <c r="I209" s="16" t="s">
+      <c r="I209" s="17" t="s">
         <v>240</v>
       </c>
     </row>
@@ -9644,7 +9651,7 @@
       <c r="F210" s="12"/>
       <c r="G210" s="12"/>
       <c r="H210" s="12"/>
-      <c r="I210" s="16" t="s">
+      <c r="I210" s="17" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9665,7 +9672,7 @@
       <c r="F211" s="12"/>
       <c r="G211" s="12"/>
       <c r="H211" s="12"/>
-      <c r="I211" s="16" t="s">
+      <c r="I211" s="17" t="s">
         <v>242</v>
       </c>
     </row>
@@ -9686,7 +9693,7 @@
       <c r="F212" s="12"/>
       <c r="G212" s="12"/>
       <c r="H212" s="12"/>
-      <c r="I212" s="16" t="s">
+      <c r="I212" s="17" t="s">
         <v>202</v>
       </c>
     </row>
@@ -9707,7 +9714,7 @@
       <c r="F213" s="12"/>
       <c r="G213" s="12"/>
       <c r="H213" s="12"/>
-      <c r="I213" s="16" t="s">
+      <c r="I213" s="17" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9728,7 +9735,7 @@
       <c r="F214" s="12"/>
       <c r="G214" s="12"/>
       <c r="H214" s="12"/>
-      <c r="I214" s="16" t="s">
+      <c r="I214" s="17" t="s">
         <v>242</v>
       </c>
     </row>
@@ -9749,7 +9756,7 @@
       <c r="F215" s="12"/>
       <c r="G215" s="12"/>
       <c r="H215" s="12"/>
-      <c r="I215" s="16" t="s">
+      <c r="I215" s="17" t="s">
         <v>202</v>
       </c>
     </row>
@@ -9770,7 +9777,7 @@
       <c r="F216" s="12"/>
       <c r="G216" s="12"/>
       <c r="H216" s="12"/>
-      <c r="I216" s="16" t="s">
+      <c r="I216" s="17" t="s">
         <v>243</v>
       </c>
     </row>
@@ -9791,7 +9798,7 @@
       <c r="F217" s="12"/>
       <c r="G217" s="12"/>
       <c r="H217" s="12"/>
-      <c r="I217" s="16" t="s">
+      <c r="I217" s="17" t="s">
         <v>244</v>
       </c>
     </row>
@@ -9812,7 +9819,7 @@
       <c r="F218" s="12"/>
       <c r="G218" s="12"/>
       <c r="H218" s="12"/>
-      <c r="I218" s="16" t="s">
+      <c r="I218" s="17" t="s">
         <v>202</v>
       </c>
     </row>
@@ -9833,7 +9840,7 @@
       <c r="F219" s="12"/>
       <c r="G219" s="12"/>
       <c r="H219" s="12"/>
-      <c r="I219" s="16" t="s">
+      <c r="I219" s="17" t="s">
         <v>243</v>
       </c>
     </row>
@@ -9854,7 +9861,7 @@
       <c r="F220" s="12"/>
       <c r="G220" s="12"/>
       <c r="H220" s="12"/>
-      <c r="I220" s="16" t="s">
+      <c r="I220" s="17" t="s">
         <v>244</v>
       </c>
     </row>
@@ -9875,7 +9882,7 @@
       <c r="F221" s="12"/>
       <c r="G221" s="12"/>
       <c r="H221" s="12"/>
-      <c r="I221" s="16" t="s">
+      <c r="I221" s="17" t="s">
         <v>245</v>
       </c>
     </row>
@@ -9896,7 +9903,7 @@
       <c r="F222" s="12"/>
       <c r="G222" s="12"/>
       <c r="H222" s="12"/>
-      <c r="I222" s="16" t="s">
+      <c r="I222" s="17" t="s">
         <v>236</v>
       </c>
     </row>
@@ -9917,7 +9924,7 @@
       <c r="F223" s="12"/>
       <c r="G223" s="12"/>
       <c r="H223" s="12"/>
-      <c r="I223" s="16" t="s">
+      <c r="I223" s="17" t="s">
         <v>246</v>
       </c>
     </row>
@@ -9938,7 +9945,7 @@
       <c r="F224" s="12"/>
       <c r="G224" s="12"/>
       <c r="H224" s="12"/>
-      <c r="I224" s="16" t="s">
+      <c r="I224" s="17" t="s">
         <v>245</v>
       </c>
     </row>
@@ -9959,7 +9966,7 @@
       <c r="F225" s="12"/>
       <c r="G225" s="12"/>
       <c r="H225" s="12"/>
-      <c r="I225" s="16" t="s">
+      <c r="I225" s="17" t="s">
         <v>236</v>
       </c>
     </row>
@@ -9980,7 +9987,7 @@
       <c r="F226" s="12"/>
       <c r="G226" s="12"/>
       <c r="H226" s="12"/>
-      <c r="I226" s="16" t="s">
+      <c r="I226" s="17" t="s">
         <v>246</v>
       </c>
     </row>
@@ -10001,7 +10008,7 @@
       <c r="F227" s="12"/>
       <c r="G227" s="12"/>
       <c r="H227" s="12"/>
-      <c r="I227" s="16" t="s">
+      <c r="I227" s="17" t="s">
         <v>245</v>
       </c>
     </row>
@@ -10028,7 +10035,7 @@
         <v>247</v>
       </c>
       <c r="H228" s="10"/>
-      <c r="I228" s="19" t="s">
+      <c r="I228" s="20" t="s">
         <v>248</v>
       </c>
       <c r="J228" s="10"/>
@@ -10056,7 +10063,7 @@
         <v>247</v>
       </c>
       <c r="H229" s="10"/>
-      <c r="I229" s="19" t="s">
+      <c r="I229" s="20" t="s">
         <v>249</v>
       </c>
       <c r="J229" s="10"/>
@@ -10084,7 +10091,7 @@
         <v>247</v>
       </c>
       <c r="H230" s="10"/>
-      <c r="I230" s="19" t="s">
+      <c r="I230" s="20" t="s">
         <v>249</v>
       </c>
       <c r="J230" s="10"/>
@@ -10112,7 +10119,7 @@
         <v>247</v>
       </c>
       <c r="H231" s="10"/>
-      <c r="I231" s="19" t="s">
+      <c r="I231" s="20" t="s">
         <v>249</v>
       </c>
       <c r="J231" s="10"/>
@@ -10140,7 +10147,7 @@
         <v>247</v>
       </c>
       <c r="H232" s="10"/>
-      <c r="I232" s="19" t="s">
+      <c r="I232" s="20" t="s">
         <v>250</v>
       </c>
       <c r="J232" s="10"/>
@@ -10168,7 +10175,7 @@
         <v>247</v>
       </c>
       <c r="H233" s="10"/>
-      <c r="I233" s="19" t="s">
+      <c r="I233" s="20" t="s">
         <v>250</v>
       </c>
       <c r="J233" s="10"/>
@@ -10196,7 +10203,7 @@
         <v>247</v>
       </c>
       <c r="H234" s="10"/>
-      <c r="I234" s="19" t="s">
+      <c r="I234" s="20" t="s">
         <v>250</v>
       </c>
       <c r="J234" s="10"/>
@@ -10224,7 +10231,7 @@
         <v>247</v>
       </c>
       <c r="H235" s="10"/>
-      <c r="I235" s="19" t="s">
+      <c r="I235" s="20" t="s">
         <v>251</v>
       </c>
       <c r="J235" s="10"/>
@@ -10252,7 +10259,7 @@
         <v>247</v>
       </c>
       <c r="H236" s="10"/>
-      <c r="I236" s="19" t="s">
+      <c r="I236" s="20" t="s">
         <v>251</v>
       </c>
       <c r="J236" s="10"/>
@@ -10280,7 +10287,7 @@
         <v>247</v>
       </c>
       <c r="H237" s="10"/>
-      <c r="I237" s="19" t="s">
+      <c r="I237" s="20" t="s">
         <v>251</v>
       </c>
       <c r="J237" s="10"/>
@@ -10308,7 +10315,7 @@
         <v>247</v>
       </c>
       <c r="H238" s="10"/>
-      <c r="I238" s="19" t="s">
+      <c r="I238" s="20" t="s">
         <v>252</v>
       </c>
       <c r="J238" s="10"/>
@@ -10336,7 +10343,7 @@
         <v>247</v>
       </c>
       <c r="H239" s="10"/>
-      <c r="I239" s="19" t="s">
+      <c r="I239" s="20" t="s">
         <v>252</v>
       </c>
       <c r="J239" s="10"/>
@@ -10364,7 +10371,7 @@
         <v>247</v>
       </c>
       <c r="H240" s="10"/>
-      <c r="I240" s="19" t="s">
+      <c r="I240" s="20" t="s">
         <v>252</v>
       </c>
       <c r="J240" s="10"/>
@@ -10392,7 +10399,7 @@
         <v>247</v>
       </c>
       <c r="H241" s="10"/>
-      <c r="I241" s="19" t="s">
+      <c r="I241" s="20" t="s">
         <v>203</v>
       </c>
       <c r="J241" s="10"/>
@@ -10420,7 +10427,7 @@
         <v>247</v>
       </c>
       <c r="H242" s="10"/>
-      <c r="I242" s="19" t="s">
+      <c r="I242" s="20" t="s">
         <v>203</v>
       </c>
       <c r="J242" s="10"/>
@@ -10448,7 +10455,7 @@
         <v>247</v>
       </c>
       <c r="H243" s="10"/>
-      <c r="I243" s="19" t="s">
+      <c r="I243" s="20" t="s">
         <v>203</v>
       </c>
       <c r="J243" s="10"/>
@@ -10476,7 +10483,7 @@
         <v>256</v>
       </c>
       <c r="H244" s="10"/>
-      <c r="I244" s="19" t="s">
+      <c r="I244" s="20" t="s">
         <v>257</v>
       </c>
       <c r="J244" s="10"/>
@@ -10504,7 +10511,7 @@
         <v>256</v>
       </c>
       <c r="H245" s="10"/>
-      <c r="I245" s="19" t="s">
+      <c r="I245" s="20" t="s">
         <v>257</v>
       </c>
       <c r="J245" s="10"/>
@@ -10532,7 +10539,7 @@
         <v>256</v>
       </c>
       <c r="H246" s="10"/>
-      <c r="I246" s="19" t="s">
+      <c r="I246" s="20" t="s">
         <v>260</v>
       </c>
       <c r="J246" s="10"/>
@@ -10560,7 +10567,7 @@
         <v>256</v>
       </c>
       <c r="H247" s="10"/>
-      <c r="I247" s="19" t="s">
+      <c r="I247" s="20" t="s">
         <v>260</v>
       </c>
       <c r="J247" s="10"/>
@@ -10588,7 +10595,7 @@
         <v>256</v>
       </c>
       <c r="H248" s="10"/>
-      <c r="I248" s="19" t="s">
+      <c r="I248" s="20" t="s">
         <v>263</v>
       </c>
       <c r="J248" s="10"/>
@@ -10616,7 +10623,7 @@
         <v>256</v>
       </c>
       <c r="H249" s="10"/>
-      <c r="I249" s="19" t="s">
+      <c r="I249" s="20" t="s">
         <v>263</v>
       </c>
       <c r="J249" s="10"/>
@@ -10644,7 +10651,7 @@
         <v>256</v>
       </c>
       <c r="H250" s="10"/>
-      <c r="I250" s="19" t="s">
+      <c r="I250" s="20" t="s">
         <v>266</v>
       </c>
       <c r="J250" s="10"/>
@@ -10672,7 +10679,7 @@
         <v>256</v>
       </c>
       <c r="H251" s="10"/>
-      <c r="I251" s="19" t="s">
+      <c r="I251" s="20" t="s">
         <v>266</v>
       </c>
       <c r="J251" s="10"/>
@@ -10700,7 +10707,7 @@
         <v>269</v>
       </c>
       <c r="H252" s="10"/>
-      <c r="I252" s="19" t="s">
+      <c r="I252" s="20" t="s">
         <v>270</v>
       </c>
       <c r="J252" s="10"/>
@@ -10728,7 +10735,7 @@
         <v>269</v>
       </c>
       <c r="H253" s="10"/>
-      <c r="I253" s="19" t="s">
+      <c r="I253" s="20" t="s">
         <v>204</v>
       </c>
       <c r="J253" s="10"/>
@@ -10756,7 +10763,7 @@
         <v>269</v>
       </c>
       <c r="H254" s="10"/>
-      <c r="I254" s="19" t="s">
+      <c r="I254" s="20" t="s">
         <v>273</v>
       </c>
       <c r="J254" s="10"/>
@@ -10784,7 +10791,7 @@
         <v>269</v>
       </c>
       <c r="H255" s="10"/>
-      <c r="I255" s="19" t="s">
+      <c r="I255" s="20" t="s">
         <v>273</v>
       </c>
       <c r="J255" s="10"/>
@@ -10812,7 +10819,7 @@
         <v>276</v>
       </c>
       <c r="H256" s="10"/>
-      <c r="I256" s="19" t="s">
+      <c r="I256" s="20" t="s">
         <v>277</v>
       </c>
       <c r="J256" s="10"/>
@@ -10840,7 +10847,7 @@
         <v>276</v>
       </c>
       <c r="H257" s="10"/>
-      <c r="I257" s="19" t="s">
+      <c r="I257" s="20" t="s">
         <v>279</v>
       </c>
       <c r="J257" s="10"/>
@@ -10868,7 +10875,7 @@
         <v>281</v>
       </c>
       <c r="H258" s="10"/>
-      <c r="I258" s="19" t="s">
+      <c r="I258" s="20" t="s">
         <v>282</v>
       </c>
       <c r="J258" s="10"/>
@@ -10896,7 +10903,7 @@
         <v>159</v>
       </c>
       <c r="H259" s="10"/>
-      <c r="I259" s="19" t="s">
+      <c r="I259" s="20" t="s">
         <v>284</v>
       </c>
       <c r="J259" s="10">
@@ -10904,394 +10911,394 @@
       </c>
     </row>
     <row r="260" spans="1:10">
-      <c r="A260" s="13">
+      <c r="A260" s="14">
         <v>259</v>
       </c>
-      <c r="B260" s="13" t="s">
+      <c r="B260" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C260" s="13" t="s">
+      <c r="C260" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D260" s="13">
-        <v>0</v>
-      </c>
-      <c r="E260" s="13" t="s">
+      <c r="D260" s="14">
+        <v>0</v>
+      </c>
+      <c r="E260" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="F260" s="13"/>
-      <c r="G260" s="13" t="s">
+      <c r="F260" s="14"/>
+      <c r="G260" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H260" s="13">
+      <c r="H260" s="14">
         <v>7</v>
       </c>
-      <c r="I260" s="13"/>
-      <c r="J260" s="13"/>
+      <c r="I260" s="14"/>
+      <c r="J260" s="14"/>
     </row>
     <row r="261" spans="1:10">
-      <c r="A261" s="13">
+      <c r="A261" s="14">
         <v>260</v>
       </c>
-      <c r="B261" s="13" t="s">
+      <c r="B261" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C261" s="13" t="s">
+      <c r="C261" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D261" s="13">
-        <v>0</v>
-      </c>
-      <c r="E261" s="13" t="s">
+      <c r="D261" s="14">
+        <v>0</v>
+      </c>
+      <c r="E261" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F261" s="13"/>
-      <c r="G261" s="13" t="s">
+      <c r="F261" s="14"/>
+      <c r="G261" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H261" s="13">
+      <c r="H261" s="14">
         <v>7</v>
       </c>
-      <c r="I261" s="13"/>
-      <c r="J261" s="13"/>
+      <c r="I261" s="14"/>
+      <c r="J261" s="14"/>
     </row>
     <row r="262" spans="1:10">
-      <c r="A262" s="13">
+      <c r="A262" s="14">
         <v>261</v>
       </c>
-      <c r="B262" s="13" t="s">
+      <c r="B262" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C262" s="13" t="s">
+      <c r="C262" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D262" s="13">
-        <v>0</v>
-      </c>
-      <c r="E262" s="13" t="s">
+      <c r="D262" s="14">
+        <v>0</v>
+      </c>
+      <c r="E262" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F262" s="13"/>
-      <c r="G262" s="13" t="s">
+      <c r="F262" s="14"/>
+      <c r="G262" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H262" s="13">
+      <c r="H262" s="14">
         <v>7</v>
       </c>
-      <c r="I262" s="13"/>
-      <c r="J262" s="13"/>
+      <c r="I262" s="14"/>
+      <c r="J262" s="14"/>
     </row>
     <row r="263" spans="1:10">
-      <c r="A263" s="13">
+      <c r="A263" s="14">
         <v>262</v>
       </c>
-      <c r="B263" s="13" t="s">
+      <c r="B263" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C263" s="13" t="s">
+      <c r="C263" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D263" s="13">
-        <v>0</v>
-      </c>
-      <c r="E263" s="13" t="s">
+      <c r="D263" s="14">
+        <v>0</v>
+      </c>
+      <c r="E263" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F263" s="13"/>
-      <c r="G263" s="13" t="s">
+      <c r="F263" s="14"/>
+      <c r="G263" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H263" s="13">
+      <c r="H263" s="14">
         <v>7</v>
       </c>
-      <c r="I263" s="13"/>
-      <c r="J263" s="13"/>
+      <c r="I263" s="14"/>
+      <c r="J263" s="14"/>
     </row>
     <row r="264" spans="1:10">
-      <c r="A264" s="13">
+      <c r="A264" s="14">
         <v>263</v>
       </c>
-      <c r="B264" s="13" t="s">
+      <c r="B264" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C264" s="13" t="s">
+      <c r="C264" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D264" s="13">
-        <v>0</v>
-      </c>
-      <c r="E264" s="13" t="s">
+      <c r="D264" s="14">
+        <v>0</v>
+      </c>
+      <c r="E264" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="F264" s="13"/>
-      <c r="G264" s="13" t="s">
+      <c r="F264" s="14"/>
+      <c r="G264" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H264" s="13">
+      <c r="H264" s="14">
         <v>7</v>
       </c>
-      <c r="I264" s="13"/>
-      <c r="J264" s="13"/>
+      <c r="I264" s="14"/>
+      <c r="J264" s="14"/>
     </row>
     <row r="265" spans="1:10">
-      <c r="A265" s="13">
+      <c r="A265" s="14">
         <v>264</v>
       </c>
-      <c r="B265" s="13" t="s">
+      <c r="B265" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C265" s="13" t="s">
+      <c r="C265" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D265" s="13">
-        <v>0</v>
-      </c>
-      <c r="E265" s="13" t="s">
+      <c r="D265" s="14">
+        <v>0</v>
+      </c>
+      <c r="E265" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="F265" s="13"/>
-      <c r="G265" s="13" t="s">
+      <c r="F265" s="14"/>
+      <c r="G265" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H265" s="13">
+      <c r="H265" s="14">
         <v>7</v>
       </c>
-      <c r="I265" s="13"/>
-      <c r="J265" s="13"/>
+      <c r="I265" s="14"/>
+      <c r="J265" s="14"/>
     </row>
     <row r="266" spans="1:10">
-      <c r="A266" s="13">
+      <c r="A266" s="14">
         <v>265</v>
       </c>
-      <c r="B266" s="13" t="s">
+      <c r="B266" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C266" s="13" t="s">
+      <c r="C266" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D266" s="13">
-        <v>0</v>
-      </c>
-      <c r="E266" s="13" t="s">
+      <c r="D266" s="14">
+        <v>0</v>
+      </c>
+      <c r="E266" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F266" s="13"/>
-      <c r="G266" s="13" t="s">
+      <c r="F266" s="14"/>
+      <c r="G266" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H266" s="13">
+      <c r="H266" s="14">
         <v>7</v>
       </c>
-      <c r="I266" s="13"/>
-      <c r="J266" s="13"/>
+      <c r="I266" s="14"/>
+      <c r="J266" s="14"/>
     </row>
     <row r="267" spans="1:10">
-      <c r="A267" s="13">
+      <c r="A267" s="14">
         <v>266</v>
       </c>
-      <c r="B267" s="13" t="s">
+      <c r="B267" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C267" s="13" t="s">
+      <c r="C267" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D267" s="13">
-        <v>0</v>
-      </c>
-      <c r="E267" s="13" t="s">
+      <c r="D267" s="14">
+        <v>0</v>
+      </c>
+      <c r="E267" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="F267" s="13"/>
-      <c r="G267" s="13" t="s">
+      <c r="F267" s="14"/>
+      <c r="G267" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H267" s="13">
+      <c r="H267" s="14">
         <v>7</v>
       </c>
-      <c r="I267" s="13"/>
-      <c r="J267" s="13"/>
+      <c r="I267" s="14"/>
+      <c r="J267" s="14"/>
     </row>
     <row r="268" spans="1:10">
-      <c r="A268" s="13">
+      <c r="A268" s="14">
         <v>267</v>
       </c>
-      <c r="B268" s="13" t="s">
+      <c r="B268" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C268" s="13" t="s">
+      <c r="C268" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D268" s="13">
-        <v>1</v>
-      </c>
-      <c r="E268" s="13" t="s">
+      <c r="D268" s="14">
+        <v>1</v>
+      </c>
+      <c r="E268" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="F268" s="13"/>
-      <c r="G268" s="13" t="s">
+      <c r="F268" s="14"/>
+      <c r="G268" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H268" s="13">
+      <c r="H268" s="14">
         <v>7</v>
       </c>
-      <c r="I268" s="13"/>
-      <c r="J268" s="13"/>
+      <c r="I268" s="14"/>
+      <c r="J268" s="14"/>
     </row>
     <row r="269" spans="1:10">
-      <c r="A269" s="13">
+      <c r="A269" s="14">
         <v>268</v>
       </c>
-      <c r="B269" s="13" t="s">
+      <c r="B269" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C269" s="13" t="s">
+      <c r="C269" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D269" s="13">
-        <v>1</v>
-      </c>
-      <c r="E269" s="13" t="s">
+      <c r="D269" s="14">
+        <v>1</v>
+      </c>
+      <c r="E269" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="F269" s="13"/>
-      <c r="G269" s="13" t="s">
+      <c r="F269" s="14"/>
+      <c r="G269" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H269" s="13">
+      <c r="H269" s="14">
         <v>7</v>
       </c>
-      <c r="I269" s="13"/>
-      <c r="J269" s="13"/>
+      <c r="I269" s="14"/>
+      <c r="J269" s="14"/>
     </row>
     <row r="270" spans="1:10">
-      <c r="A270" s="13">
+      <c r="A270" s="14">
         <v>269</v>
       </c>
-      <c r="B270" s="13" t="s">
+      <c r="B270" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C270" s="13" t="s">
+      <c r="C270" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D270" s="13">
-        <v>1</v>
-      </c>
-      <c r="E270" s="13" t="s">
+      <c r="D270" s="14">
+        <v>1</v>
+      </c>
+      <c r="E270" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="F270" s="13"/>
-      <c r="G270" s="13" t="s">
+      <c r="F270" s="14"/>
+      <c r="G270" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H270" s="13">
+      <c r="H270" s="14">
         <v>7</v>
       </c>
-      <c r="I270" s="13"/>
-      <c r="J270" s="13"/>
+      <c r="I270" s="14"/>
+      <c r="J270" s="14"/>
     </row>
     <row r="271" spans="1:10">
-      <c r="A271" s="13">
+      <c r="A271" s="14">
         <v>270</v>
       </c>
-      <c r="B271" s="13" t="s">
+      <c r="B271" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C271" s="13" t="s">
+      <c r="C271" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D271" s="13">
-        <v>1</v>
-      </c>
-      <c r="E271" s="13" t="s">
+      <c r="D271" s="14">
+        <v>1</v>
+      </c>
+      <c r="E271" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="F271" s="13"/>
-      <c r="G271" s="13" t="s">
+      <c r="F271" s="14"/>
+      <c r="G271" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H271" s="13">
+      <c r="H271" s="14">
         <v>7</v>
       </c>
-      <c r="I271" s="13"/>
-      <c r="J271" s="13"/>
+      <c r="I271" s="14"/>
+      <c r="J271" s="14"/>
     </row>
     <row r="272" spans="1:10">
-      <c r="A272" s="13">
+      <c r="A272" s="14">
         <v>271</v>
       </c>
-      <c r="B272" s="13" t="s">
+      <c r="B272" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C272" s="13" t="s">
+      <c r="C272" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D272" s="13">
-        <v>2</v>
-      </c>
-      <c r="E272" s="13" t="s">
+      <c r="D272" s="14">
+        <v>2</v>
+      </c>
+      <c r="E272" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="F272" s="13"/>
-      <c r="G272" s="13" t="s">
+      <c r="F272" s="14"/>
+      <c r="G272" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="H272" s="13">
+      <c r="H272" s="14">
         <v>7</v>
       </c>
-      <c r="I272" s="13"/>
-      <c r="J272" s="13"/>
+      <c r="I272" s="14"/>
+      <c r="J272" s="14"/>
     </row>
     <row r="273" spans="1:10">
-      <c r="A273" s="13">
+      <c r="A273" s="14">
         <v>272</v>
       </c>
-      <c r="B273" s="13" t="s">
+      <c r="B273" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C273" s="13" t="s">
+      <c r="C273" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D273" s="13">
-        <v>2</v>
-      </c>
-      <c r="E273" s="13" t="s">
+      <c r="D273" s="14">
+        <v>2</v>
+      </c>
+      <c r="E273" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="F273" s="13"/>
-      <c r="G273" s="13" t="s">
+      <c r="F273" s="14"/>
+      <c r="G273" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="H273" s="13">
+      <c r="H273" s="14">
         <v>7</v>
       </c>
-      <c r="I273" s="13"/>
-      <c r="J273" s="13"/>
+      <c r="I273" s="14"/>
+      <c r="J273" s="14"/>
     </row>
     <row r="274" spans="1:10">
-      <c r="A274" s="13">
+      <c r="A274" s="14">
         <v>273</v>
       </c>
-      <c r="B274" s="13" t="s">
+      <c r="B274" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C274" s="13" t="s">
+      <c r="C274" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D274" s="13">
+      <c r="D274" s="14">
         <v>3</v>
       </c>
-      <c r="E274" s="13" t="s">
+      <c r="E274" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="F274" s="13"/>
-      <c r="G274" s="13" t="s">
+      <c r="F274" s="14"/>
+      <c r="G274" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="H274" s="13">
+      <c r="H274" s="14">
         <v>7</v>
       </c>
-      <c r="I274" s="13"/>
-      <c r="J274" s="13">
+      <c r="I274" s="14"/>
+      <c r="J274" s="14">
         <v>1</v>
       </c>
     </row>
@@ -23629,7 +23636,7 @@
         <v>73</v>
       </c>
       <c r="H493" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I493" s="5"/>
     </row>
@@ -23645,7 +23652,7 @@
         <v>319</v>
       </c>
       <c r="D494" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E494" s="5"/>
       <c r="F494" s="5" t="s">
@@ -23671,7 +23678,7 @@
         <v>344</v>
       </c>
       <c r="D495" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E495" s="5"/>
       <c r="F495" s="5" t="s">
@@ -23681,7 +23688,7 @@
         <v>85</v>
       </c>
       <c r="H495" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I495" s="5"/>
     </row>
@@ -23749,7 +23756,7 @@
         <v>376</v>
       </c>
       <c r="D498" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E498" s="5"/>
       <c r="F498" s="5" t="s">
@@ -23769,17 +23776,21 @@
         <v>181</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C499" s="5"/>
+        <v>464</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>465</v>
+      </c>
       <c r="D499" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E499" s="5"/>
       <c r="F499" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G499" s="5"/>
+        <v>422</v>
+      </c>
+      <c r="G499" s="5" t="s">
+        <v>423</v>
+      </c>
       <c r="H499" s="5">
         <v>0</v>
       </c>
@@ -23791,17 +23802,21 @@
         <v>181</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C500" s="5"/>
+        <v>471</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="D500" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E500" s="5"/>
       <c r="F500" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G500" s="5"/>
+        <v>466</v>
+      </c>
+      <c r="G500" s="5" t="s">
+        <v>467</v>
+      </c>
       <c r="H500" s="5">
         <v>0</v>
       </c>
@@ -23813,19 +23828,23 @@
         <v>181</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C501" s="5"/>
+        <v>343</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>344</v>
+      </c>
       <c r="D501" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E501" s="5"/>
       <c r="F501" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G501" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="G501" s="5" t="s">
+        <v>376</v>
+      </c>
       <c r="H501" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I501" s="5"/>
     </row>
@@ -23834,19 +23853,23 @@
         <v>182</v>
       </c>
       <c r="B502" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C502" s="10"/>
+        <v>464</v>
+      </c>
+      <c r="C502" s="10" t="s">
+        <v>465</v>
+      </c>
       <c r="D502" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E502" s="10"/>
       <c r="F502" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G502" s="10"/>
+        <v>428</v>
+      </c>
+      <c r="G502" s="10" t="s">
+        <v>427</v>
+      </c>
       <c r="H502" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I502" s="10"/>
     </row>
@@ -23855,17 +23878,21 @@
         <v>183</v>
       </c>
       <c r="B503" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C503" s="10"/>
+        <v>318</v>
+      </c>
+      <c r="C503" s="10" t="s">
+        <v>319</v>
+      </c>
       <c r="D503" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E503" s="10"/>
       <c r="F503" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G503" s="10"/>
+        <v>471</v>
+      </c>
+      <c r="G503" s="10" t="s">
+        <v>346</v>
+      </c>
       <c r="H503" s="10">
         <v>0</v>
       </c>
@@ -23876,20 +23903,20 @@
         <v>184</v>
       </c>
       <c r="B504" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C504" s="10"/>
-      <c r="D504" s="10">
-        <v>0</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C504" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D504" s="10"/>
       <c r="E504" s="10"/>
       <c r="F504" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G504" s="10"/>
-      <c r="H504" s="10">
-        <v>0</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="G504" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="H504" s="10"/>
       <c r="I504" s="10"/>
     </row>
     <row r="505" spans="1:9">
@@ -23897,20 +23924,20 @@
         <v>185</v>
       </c>
       <c r="B505" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C505" s="10"/>
-      <c r="D505" s="10">
-        <v>0</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C505" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D505" s="10"/>
       <c r="E505" s="10"/>
       <c r="F505" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G505" s="10"/>
-      <c r="H505" s="10">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G505" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H505" s="10"/>
       <c r="I505" s="10"/>
     </row>
     <row r="506" spans="1:9">
@@ -23918,20 +23945,20 @@
         <v>186</v>
       </c>
       <c r="B506" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C506" s="10"/>
-      <c r="D506" s="10">
-        <v>0</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C506" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D506" s="10"/>
       <c r="E506" s="10"/>
       <c r="F506" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G506" s="10"/>
-      <c r="H506" s="10">
-        <v>0</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="G506" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H506" s="10"/>
       <c r="I506" s="10"/>
     </row>
     <row r="507" spans="1:9">
@@ -23942,17 +23969,13 @@
         <v>15</v>
       </c>
       <c r="C507" s="10"/>
-      <c r="D507" s="10">
-        <v>0</v>
-      </c>
+      <c r="D507" s="10"/>
       <c r="E507" s="10"/>
       <c r="F507" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G507" s="10"/>
-      <c r="H507" s="10">
-        <v>0</v>
-      </c>
+      <c r="H507" s="10"/>
       <c r="I507" s="10"/>
     </row>
     <row r="508" spans="1:9">
@@ -23963,17 +23986,13 @@
         <v>15</v>
       </c>
       <c r="C508" s="10"/>
-      <c r="D508" s="10">
-        <v>0</v>
-      </c>
+      <c r="D508" s="10"/>
       <c r="E508" s="10"/>
       <c r="F508" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G508" s="10"/>
-      <c r="H508" s="10">
-        <v>0</v>
-      </c>
+      <c r="H508" s="10"/>
       <c r="I508" s="10"/>
     </row>
     <row r="509" spans="1:9">
@@ -24036,7 +24055,9 @@
       <c r="C511" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="D511" s="12"/>
+      <c r="D511" s="12">
+        <v>1</v>
+      </c>
       <c r="E511" s="12"/>
       <c r="F511" s="12" t="s">
         <v>475</v>
@@ -24044,7 +24065,9 @@
       <c r="G511" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="H511" s="12"/>
+      <c r="H511" s="12">
+        <v>1</v>
+      </c>
       <c r="I511" s="12"/>
     </row>
     <row r="512" spans="1:9">
@@ -24057,7 +24080,9 @@
       <c r="C512" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="D512" s="12"/>
+      <c r="D512" s="12">
+        <v>1</v>
+      </c>
       <c r="E512" s="12"/>
       <c r="F512" s="12" t="s">
         <v>477</v>
@@ -24065,7 +24090,9 @@
       <c r="G512" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="H512" s="12"/>
+      <c r="H512" s="12">
+        <v>0</v>
+      </c>
       <c r="I512" s="12"/>
     </row>
     <row r="513" spans="1:9">
@@ -24111,138 +24138,146 @@
       <c r="I514" s="12"/>
     </row>
     <row r="515" spans="1:9">
-      <c r="A515" s="12">
+      <c r="A515" s="13">
         <v>192</v>
       </c>
-      <c r="B515" s="12" t="s">
+      <c r="B515" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="C515" s="12" t="s">
+      <c r="C515" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="D515" s="12">
-        <v>1</v>
-      </c>
-      <c r="E515" s="12"/>
-      <c r="F515" s="12" t="s">
+      <c r="D515" s="13">
+        <v>1</v>
+      </c>
+      <c r="E515" s="13"/>
+      <c r="F515" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="G515" s="12" t="s">
+      <c r="G515" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="H515" s="12">
-        <v>1</v>
-      </c>
-      <c r="I515" s="12"/>
+      <c r="H515" s="13">
+        <v>1</v>
+      </c>
+      <c r="I515" s="13"/>
     </row>
     <row r="516" spans="1:9">
-      <c r="A516" s="12">
+      <c r="A516" s="13">
         <v>193</v>
       </c>
-      <c r="B516" s="12" t="s">
+      <c r="B516" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="C516" s="12" t="s">
+      <c r="C516" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="D516" s="12">
-        <v>1</v>
-      </c>
-      <c r="E516" s="12"/>
-      <c r="F516" s="12" t="s">
+      <c r="D516" s="13">
+        <v>1</v>
+      </c>
+      <c r="E516" s="13"/>
+      <c r="F516" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="G516" s="12" t="s">
+      <c r="G516" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="H516" s="12">
-        <v>1</v>
-      </c>
-      <c r="I516" s="12"/>
+      <c r="H516" s="13">
+        <v>1</v>
+      </c>
+      <c r="I516" s="13"/>
     </row>
     <row r="517" spans="1:9">
-      <c r="A517" s="12">
+      <c r="A517" s="13">
         <v>194</v>
       </c>
-      <c r="B517" s="12" t="s">
+      <c r="B517" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="C517" s="12" t="s">
+      <c r="C517" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="D517" s="12"/>
-      <c r="E517" s="12"/>
-      <c r="F517" s="12" t="s">
+      <c r="D517" s="13">
+        <v>4</v>
+      </c>
+      <c r="E517" s="13"/>
+      <c r="F517" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="G517" s="12" t="s">
+      <c r="G517" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="H517" s="12"/>
-      <c r="I517" s="12"/>
+      <c r="H517" s="13">
+        <v>1</v>
+      </c>
+      <c r="I517" s="13"/>
     </row>
     <row r="518" spans="1:9">
-      <c r="A518" s="12">
+      <c r="A518" s="13">
         <v>194</v>
       </c>
-      <c r="B518" s="12" t="s">
+      <c r="B518" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="C518" s="12" t="s">
+      <c r="C518" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="D518" s="12"/>
-      <c r="E518" s="12"/>
-      <c r="F518" s="12" t="s">
+      <c r="D518" s="13">
+        <v>6</v>
+      </c>
+      <c r="E518" s="13"/>
+      <c r="F518" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="G518" s="12" t="s">
+      <c r="G518" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H518" s="12"/>
-      <c r="I518" s="12"/>
+      <c r="H518" s="13">
+        <v>0</v>
+      </c>
+      <c r="I518" s="13"/>
     </row>
     <row r="519" spans="1:9">
-      <c r="A519" s="12">
+      <c r="A519" s="13">
         <v>195</v>
       </c>
-      <c r="B519" s="12" t="s">
+      <c r="B519" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="C519" s="12" t="s">
+      <c r="C519" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="D519" s="12"/>
-      <c r="E519" s="12"/>
-      <c r="F519" s="12" t="s">
+      <c r="D519" s="13"/>
+      <c r="E519" s="13"/>
+      <c r="F519" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="G519" s="12" t="s">
+      <c r="G519" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="H519" s="12"/>
-      <c r="I519" s="12"/>
+      <c r="H519" s="13"/>
+      <c r="I519" s="13"/>
     </row>
     <row r="520" spans="1:9">
-      <c r="A520" s="12">
+      <c r="A520" s="13">
         <v>195</v>
       </c>
-      <c r="B520" s="12" t="s">
+      <c r="B520" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C520" s="12" t="s">
+      <c r="C520" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="D520" s="12"/>
-      <c r="E520" s="12"/>
-      <c r="F520" s="12" t="s">
+      <c r="D520" s="13"/>
+      <c r="E520" s="13"/>
+      <c r="F520" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="G520" s="12" t="s">
+      <c r="G520" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H520" s="12"/>
-      <c r="I520" s="12"/>
+      <c r="H520" s="13"/>
+      <c r="I520" s="13"/>
     </row>
     <row r="521" spans="1:9">
       <c r="A521" s="12">
@@ -24379,138 +24414,138 @@
       <c r="I526" s="12"/>
     </row>
     <row r="527" spans="1:9">
-      <c r="A527" s="12">
+      <c r="A527" s="13">
         <v>199</v>
       </c>
-      <c r="B527" s="12" t="s">
+      <c r="B527" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C527" s="12" t="s">
+      <c r="C527" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="D527" s="12">
+      <c r="D527" s="13">
         <v>4</v>
       </c>
-      <c r="E527" s="12"/>
-      <c r="F527" s="12" t="s">
+      <c r="E527" s="13"/>
+      <c r="F527" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="G527" s="12" t="s">
+      <c r="G527" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="H527" s="12">
-        <v>1</v>
-      </c>
-      <c r="I527" s="12"/>
+      <c r="H527" s="13">
+        <v>1</v>
+      </c>
+      <c r="I527" s="13"/>
     </row>
     <row r="528" spans="1:9">
-      <c r="A528" s="12">
+      <c r="A528" s="13">
         <v>200</v>
       </c>
-      <c r="B528" s="12" t="s">
+      <c r="B528" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="C528" s="12" t="s">
+      <c r="C528" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="D528" s="12">
-        <v>2</v>
-      </c>
-      <c r="E528" s="12"/>
-      <c r="F528" s="12" t="s">
+      <c r="D528" s="13">
+        <v>2</v>
+      </c>
+      <c r="E528" s="13"/>
+      <c r="F528" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="G528" s="12" t="s">
+      <c r="G528" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="H528" s="12">
-        <v>0</v>
-      </c>
-      <c r="I528" s="12"/>
+      <c r="H528" s="13">
+        <v>0</v>
+      </c>
+      <c r="I528" s="13"/>
     </row>
     <row r="529" spans="1:9">
-      <c r="A529" s="12">
+      <c r="A529" s="13">
         <v>201</v>
       </c>
-      <c r="B529" s="12" t="s">
+      <c r="B529" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C529" s="12" t="s">
+      <c r="C529" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="D529" s="12"/>
-      <c r="E529" s="12"/>
-      <c r="F529" s="12" t="s">
+      <c r="D529" s="13"/>
+      <c r="E529" s="13"/>
+      <c r="F529" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="G529" s="12" t="s">
+      <c r="G529" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="H529" s="12"/>
-      <c r="I529" s="12"/>
+      <c r="H529" s="13"/>
+      <c r="I529" s="13"/>
     </row>
     <row r="530" spans="1:9">
-      <c r="A530" s="12">
+      <c r="A530" s="13">
         <v>201</v>
       </c>
-      <c r="B530" s="12" t="s">
+      <c r="B530" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="C530" s="12" t="s">
+      <c r="C530" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="D530" s="12"/>
-      <c r="E530" s="12"/>
-      <c r="F530" s="12" t="s">
+      <c r="D530" s="13"/>
+      <c r="E530" s="13"/>
+      <c r="F530" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="G530" s="12" t="s">
+      <c r="G530" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="H530" s="12"/>
-      <c r="I530" s="12"/>
+      <c r="H530" s="13"/>
+      <c r="I530" s="13"/>
     </row>
     <row r="531" spans="1:9">
-      <c r="A531" s="12">
+      <c r="A531" s="13">
         <v>202</v>
       </c>
-      <c r="B531" s="12" t="s">
+      <c r="B531" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="C531" s="12" t="s">
+      <c r="C531" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="D531" s="12"/>
-      <c r="E531" s="12"/>
-      <c r="F531" s="12" t="s">
+      <c r="D531" s="13"/>
+      <c r="E531" s="13"/>
+      <c r="F531" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G531" s="12" t="s">
+      <c r="G531" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="H531" s="12"/>
-      <c r="I531" s="12"/>
+      <c r="H531" s="13"/>
+      <c r="I531" s="13"/>
     </row>
     <row r="532" spans="1:9">
-      <c r="A532" s="12">
+      <c r="A532" s="13">
         <v>202</v>
       </c>
-      <c r="B532" s="12" t="s">
+      <c r="B532" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="C532" s="12" t="s">
+      <c r="C532" s="13" t="s">
         <v>499</v>
       </c>
-      <c r="D532" s="12"/>
-      <c r="E532" s="12"/>
-      <c r="F532" s="12" t="s">
+      <c r="D532" s="13"/>
+      <c r="E532" s="13"/>
+      <c r="F532" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="G532" s="12" t="s">
+      <c r="G532" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="H532" s="12"/>
-      <c r="I532" s="12"/>
+      <c r="H532" s="13"/>
+      <c r="I532" s="13"/>
     </row>
     <row r="533" spans="1:9">
       <c r="A533" s="12">
@@ -24522,7 +24557,9 @@
       <c r="C533" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="D533" s="12"/>
+      <c r="D533" s="12">
+        <v>7</v>
+      </c>
       <c r="E533" s="12"/>
       <c r="F533" s="12" t="s">
         <v>506</v>
@@ -24530,7 +24567,9 @@
       <c r="G533" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="H533" s="12"/>
+      <c r="H533" s="12">
+        <v>1</v>
+      </c>
       <c r="I533" s="12"/>
     </row>
     <row r="534" spans="1:9">
@@ -24543,7 +24582,9 @@
       <c r="C534" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="D534" s="12"/>
+      <c r="D534" s="12">
+        <v>1</v>
+      </c>
       <c r="E534" s="12"/>
       <c r="F534" s="12" t="s">
         <v>510</v>
@@ -24551,7 +24592,9 @@
       <c r="G534" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="H534" s="12"/>
+      <c r="H534" s="12">
+        <v>0</v>
+      </c>
       <c r="I534" s="12"/>
     </row>
     <row r="535" spans="1:9">
@@ -24639,130 +24682,138 @@
       <c r="I538" s="12"/>
     </row>
     <row r="539" spans="1:9">
-      <c r="A539" s="12">
+      <c r="A539" s="13">
         <v>206</v>
       </c>
-      <c r="B539" s="12" t="s">
+      <c r="B539" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="C539" s="12" t="s">
+      <c r="C539" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="D539" s="12"/>
-      <c r="E539" s="12"/>
-      <c r="F539" s="12" t="s">
+      <c r="D539" s="13">
+        <v>2</v>
+      </c>
+      <c r="E539" s="13"/>
+      <c r="F539" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="G539" s="12" t="s">
+      <c r="G539" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="H539" s="12"/>
-      <c r="I539" s="12"/>
+      <c r="H539" s="13">
+        <v>2</v>
+      </c>
+      <c r="I539" s="13"/>
     </row>
     <row r="540" spans="1:9">
-      <c r="A540" s="12">
+      <c r="A540" s="13">
         <v>206</v>
       </c>
-      <c r="B540" s="12" t="s">
+      <c r="B540" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="C540" s="12" t="s">
+      <c r="C540" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="D540" s="12"/>
-      <c r="E540" s="12"/>
-      <c r="F540" s="12" t="s">
+      <c r="D540" s="13">
+        <v>5</v>
+      </c>
+      <c r="E540" s="13"/>
+      <c r="F540" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="G540" s="12" t="s">
+      <c r="G540" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="H540" s="12"/>
-      <c r="I540" s="12"/>
+      <c r="H540" s="13">
+        <v>1</v>
+      </c>
+      <c r="I540" s="13"/>
     </row>
     <row r="541" spans="1:9">
-      <c r="A541" s="12">
+      <c r="A541" s="13">
         <v>207</v>
       </c>
-      <c r="B541" s="12" t="s">
+      <c r="B541" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="C541" s="12" t="s">
+      <c r="C541" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="D541" s="12"/>
-      <c r="E541" s="12"/>
-      <c r="F541" s="12" t="s">
+      <c r="D541" s="13"/>
+      <c r="E541" s="13"/>
+      <c r="F541" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="G541" s="12" t="s">
+      <c r="G541" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="H541" s="12"/>
-      <c r="I541" s="12"/>
+      <c r="H541" s="13"/>
+      <c r="I541" s="13"/>
     </row>
     <row r="542" spans="1:9">
-      <c r="A542" s="12">
+      <c r="A542" s="13">
         <v>207</v>
       </c>
-      <c r="B542" s="12" t="s">
+      <c r="B542" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="C542" s="12" t="s">
+      <c r="C542" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="D542" s="12"/>
-      <c r="E542" s="12"/>
-      <c r="F542" s="12" t="s">
+      <c r="D542" s="13"/>
+      <c r="E542" s="13"/>
+      <c r="F542" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="G542" s="12" t="s">
+      <c r="G542" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="H542" s="12"/>
-      <c r="I542" s="12"/>
+      <c r="H542" s="13"/>
+      <c r="I542" s="13"/>
     </row>
     <row r="543" spans="1:9">
-      <c r="A543" s="12">
+      <c r="A543" s="13">
         <v>208</v>
       </c>
-      <c r="B543" s="12" t="s">
+      <c r="B543" s="13" t="s">
         <v>514</v>
       </c>
-      <c r="C543" s="12" t="s">
+      <c r="C543" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="D543" s="12"/>
-      <c r="E543" s="12"/>
-      <c r="F543" s="12" t="s">
+      <c r="D543" s="13"/>
+      <c r="E543" s="13"/>
+      <c r="F543" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="G543" s="12" t="s">
+      <c r="G543" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="H543" s="12"/>
-      <c r="I543" s="12"/>
+      <c r="H543" s="13"/>
+      <c r="I543" s="13"/>
     </row>
     <row r="544" spans="1:9">
-      <c r="A544" s="12">
+      <c r="A544" s="13">
         <v>208</v>
       </c>
-      <c r="B544" s="12" t="s">
+      <c r="B544" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="C544" s="12" t="s">
+      <c r="C544" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="D544" s="12"/>
-      <c r="E544" s="12"/>
-      <c r="F544" s="12" t="s">
+      <c r="D544" s="13"/>
+      <c r="E544" s="13"/>
+      <c r="F544" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="G544" s="12" t="s">
+      <c r="G544" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="H544" s="12"/>
-      <c r="I544" s="12"/>
+      <c r="H544" s="13"/>
+      <c r="I544" s="13"/>
     </row>
     <row r="545" spans="1:9">
       <c r="A545" s="12">
@@ -24774,7 +24825,9 @@
       <c r="C545" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="D545" s="12"/>
+      <c r="D545" s="12">
+        <v>1</v>
+      </c>
       <c r="E545" s="12"/>
       <c r="F545" s="12" t="s">
         <v>522</v>
@@ -24782,7 +24835,9 @@
       <c r="G545" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="H545" s="12"/>
+      <c r="H545" s="12">
+        <v>1</v>
+      </c>
       <c r="I545" s="12"/>
     </row>
     <row r="546" spans="1:9">
@@ -24795,7 +24850,9 @@
       <c r="C546" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="D546" s="12"/>
+      <c r="D546" s="12">
+        <v>2</v>
+      </c>
       <c r="E546" s="12"/>
       <c r="F546" s="12" t="s">
         <v>526</v>
@@ -24803,7 +24860,9 @@
       <c r="G546" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="H546" s="12"/>
+      <c r="H546" s="12">
+        <v>2</v>
+      </c>
       <c r="I546" s="12"/>
     </row>
     <row r="547" spans="1:9">
@@ -24891,130 +24950,138 @@
       <c r="I550" s="12"/>
     </row>
     <row r="551" spans="1:9">
-      <c r="A551" s="12">
+      <c r="A551" s="13">
         <v>212</v>
       </c>
-      <c r="B551" s="12" t="s">
+      <c r="B551" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="C551" s="12" t="s">
+      <c r="C551" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="D551" s="12"/>
-      <c r="E551" s="12"/>
-      <c r="F551" s="12" t="s">
+      <c r="D551" s="13">
+        <v>0</v>
+      </c>
+      <c r="E551" s="13"/>
+      <c r="F551" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="G551" s="12" t="s">
+      <c r="G551" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="H551" s="12"/>
-      <c r="I551" s="12"/>
+      <c r="H551" s="13">
+        <v>0</v>
+      </c>
+      <c r="I551" s="13"/>
     </row>
     <row r="552" spans="1:9">
-      <c r="A552" s="12">
+      <c r="A552" s="13">
         <v>212</v>
       </c>
-      <c r="B552" s="12" t="s">
+      <c r="B552" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="C552" s="12" t="s">
+      <c r="C552" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="D552" s="12"/>
-      <c r="E552" s="12"/>
-      <c r="F552" s="12" t="s">
+      <c r="D552" s="13">
+        <v>1</v>
+      </c>
+      <c r="E552" s="13"/>
+      <c r="F552" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="G552" s="12" t="s">
+      <c r="G552" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="H552" s="12"/>
-      <c r="I552" s="12"/>
+      <c r="H552" s="13">
+        <v>1</v>
+      </c>
+      <c r="I552" s="13"/>
     </row>
     <row r="553" spans="1:9">
-      <c r="A553" s="12">
+      <c r="A553" s="13">
         <v>213</v>
       </c>
-      <c r="B553" s="12" t="s">
+      <c r="B553" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="C553" s="12" t="s">
+      <c r="C553" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="D553" s="12"/>
-      <c r="E553" s="12"/>
-      <c r="F553" s="12" t="s">
+      <c r="D553" s="13"/>
+      <c r="E553" s="13"/>
+      <c r="F553" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="G553" s="12" t="s">
+      <c r="G553" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="H553" s="12"/>
-      <c r="I553" s="12"/>
+      <c r="H553" s="13"/>
+      <c r="I553" s="13"/>
     </row>
     <row r="554" spans="1:9">
-      <c r="A554" s="12">
+      <c r="A554" s="13">
         <v>213</v>
       </c>
-      <c r="B554" s="12" t="s">
+      <c r="B554" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="C554" s="12" t="s">
+      <c r="C554" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="D554" s="12"/>
-      <c r="E554" s="12"/>
-      <c r="F554" s="12" t="s">
+      <c r="D554" s="13"/>
+      <c r="E554" s="13"/>
+      <c r="F554" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="G554" s="12" t="s">
+      <c r="G554" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="H554" s="12"/>
-      <c r="I554" s="12"/>
+      <c r="H554" s="13"/>
+      <c r="I554" s="13"/>
     </row>
     <row r="555" spans="1:9">
-      <c r="A555" s="12">
+      <c r="A555" s="13">
         <v>214</v>
       </c>
-      <c r="B555" s="12" t="s">
+      <c r="B555" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="C555" s="12" t="s">
+      <c r="C555" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="D555" s="12"/>
-      <c r="E555" s="12"/>
-      <c r="F555" s="12" t="s">
+      <c r="D555" s="13"/>
+      <c r="E555" s="13"/>
+      <c r="F555" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="G555" s="12" t="s">
+      <c r="G555" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="H555" s="12"/>
-      <c r="I555" s="12"/>
+      <c r="H555" s="13"/>
+      <c r="I555" s="13"/>
     </row>
     <row r="556" spans="1:9">
-      <c r="A556" s="12">
+      <c r="A556" s="13">
         <v>214</v>
       </c>
-      <c r="B556" s="12" t="s">
+      <c r="B556" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="C556" s="12" t="s">
+      <c r="C556" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="D556" s="12"/>
-      <c r="E556" s="12"/>
-      <c r="F556" s="12" t="s">
+      <c r="D556" s="13"/>
+      <c r="E556" s="13"/>
+      <c r="F556" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="G556" s="12" t="s">
+      <c r="G556" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="H556" s="12"/>
-      <c r="I556" s="12"/>
+      <c r="H556" s="13"/>
+      <c r="I556" s="13"/>
     </row>
     <row r="557" spans="1:9">
       <c r="A557" s="12">
@@ -25026,7 +25093,9 @@
       <c r="C557" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="D557" s="12"/>
+      <c r="D557" s="12">
+        <v>3</v>
+      </c>
       <c r="E557" s="12"/>
       <c r="F557" s="12" t="s">
         <v>538</v>
@@ -25034,7 +25103,9 @@
       <c r="G557" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="H557" s="12"/>
+      <c r="H557" s="12">
+        <v>1</v>
+      </c>
       <c r="I557" s="12"/>
     </row>
     <row r="558" spans="1:9">
@@ -25047,7 +25118,9 @@
       <c r="C558" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="D558" s="12"/>
+      <c r="D558" s="12">
+        <v>1</v>
+      </c>
       <c r="E558" s="12"/>
       <c r="F558" s="12" t="s">
         <v>542</v>
@@ -25055,7 +25128,9 @@
       <c r="G558" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="H558" s="12"/>
+      <c r="H558" s="12">
+        <v>4</v>
+      </c>
       <c r="I558" s="12"/>
     </row>
     <row r="559" spans="1:9">
@@ -25143,130 +25218,138 @@
       <c r="I562" s="12"/>
     </row>
     <row r="563" spans="1:9">
-      <c r="A563" s="12">
+      <c r="A563" s="13">
         <v>218</v>
       </c>
-      <c r="B563" s="12" t="s">
+      <c r="B563" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="C563" s="12" t="s">
+      <c r="C563" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="D563" s="12"/>
-      <c r="E563" s="12"/>
-      <c r="F563" s="12" t="s">
+      <c r="D563" s="13">
+        <v>3</v>
+      </c>
+      <c r="E563" s="13"/>
+      <c r="F563" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="G563" s="12" t="s">
+      <c r="G563" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="H563" s="12"/>
-      <c r="I563" s="12"/>
+      <c r="H563" s="13">
+        <v>0</v>
+      </c>
+      <c r="I563" s="13"/>
     </row>
     <row r="564" spans="1:9">
-      <c r="A564" s="12">
+      <c r="A564" s="13">
         <v>218</v>
       </c>
-      <c r="B564" s="12" t="s">
+      <c r="B564" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="C564" s="12" t="s">
+      <c r="C564" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="D564" s="12"/>
-      <c r="E564" s="12"/>
-      <c r="F564" s="12" t="s">
+      <c r="D564" s="13">
+        <v>3</v>
+      </c>
+      <c r="E564" s="13"/>
+      <c r="F564" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="G564" s="12" t="s">
+      <c r="G564" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="H564" s="12"/>
-      <c r="I564" s="12"/>
+      <c r="H564" s="13">
+        <v>1</v>
+      </c>
+      <c r="I564" s="13"/>
     </row>
     <row r="565" spans="1:9">
-      <c r="A565" s="12">
+      <c r="A565" s="13">
         <v>219</v>
       </c>
-      <c r="B565" s="12" t="s">
+      <c r="B565" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="C565" s="12" t="s">
+      <c r="C565" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="D565" s="12"/>
-      <c r="E565" s="12"/>
-      <c r="F565" s="12" t="s">
+      <c r="D565" s="13"/>
+      <c r="E565" s="13"/>
+      <c r="F565" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="G565" s="12" t="s">
+      <c r="G565" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="H565" s="12"/>
-      <c r="I565" s="12"/>
+      <c r="H565" s="13"/>
+      <c r="I565" s="13"/>
     </row>
     <row r="566" spans="1:9">
-      <c r="A566" s="12">
+      <c r="A566" s="13">
         <v>219</v>
       </c>
-      <c r="B566" s="12" t="s">
+      <c r="B566" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="C566" s="12" t="s">
+      <c r="C566" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="D566" s="12"/>
-      <c r="E566" s="12"/>
-      <c r="F566" s="12" t="s">
+      <c r="D566" s="13"/>
+      <c r="E566" s="13"/>
+      <c r="F566" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="G566" s="12" t="s">
+      <c r="G566" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="H566" s="12"/>
-      <c r="I566" s="12"/>
+      <c r="H566" s="13"/>
+      <c r="I566" s="13"/>
     </row>
     <row r="567" spans="1:9">
-      <c r="A567" s="12">
+      <c r="A567" s="13">
         <v>220</v>
       </c>
-      <c r="B567" s="12" t="s">
+      <c r="B567" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="C567" s="12" t="s">
+      <c r="C567" s="13" t="s">
         <v>547</v>
       </c>
-      <c r="D567" s="12"/>
-      <c r="E567" s="12"/>
-      <c r="F567" s="12" t="s">
+      <c r="D567" s="13"/>
+      <c r="E567" s="13"/>
+      <c r="F567" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="G567" s="12" t="s">
+      <c r="G567" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="H567" s="12"/>
-      <c r="I567" s="12"/>
+      <c r="H567" s="13"/>
+      <c r="I567" s="13"/>
     </row>
     <row r="568" spans="1:9">
-      <c r="A568" s="12">
+      <c r="A568" s="13">
         <v>220</v>
       </c>
-      <c r="B568" s="12" t="s">
+      <c r="B568" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="C568" s="12" t="s">
+      <c r="C568" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="D568" s="12"/>
-      <c r="E568" s="12"/>
-      <c r="F568" s="12" t="s">
+      <c r="D568" s="13"/>
+      <c r="E568" s="13"/>
+      <c r="F568" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="G568" s="12" t="s">
+      <c r="G568" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="H568" s="12"/>
-      <c r="I568" s="12"/>
+      <c r="H568" s="13"/>
+      <c r="I568" s="13"/>
     </row>
     <row r="569" spans="1:9">
       <c r="A569" s="12">
@@ -25278,7 +25361,9 @@
       <c r="C569" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="D569" s="12"/>
+      <c r="D569" s="12">
+        <v>1</v>
+      </c>
       <c r="E569" s="12"/>
       <c r="F569" s="12" t="s">
         <v>554</v>
@@ -25286,7 +25371,9 @@
       <c r="G569" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="H569" s="12"/>
+      <c r="H569" s="12">
+        <v>1</v>
+      </c>
       <c r="I569" s="12"/>
     </row>
     <row r="570" spans="1:9">
@@ -25299,7 +25386,9 @@
       <c r="C570" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="D570" s="12"/>
+      <c r="D570" s="12">
+        <v>1</v>
+      </c>
       <c r="E570" s="12"/>
       <c r="F570" s="12" t="s">
         <v>558</v>
@@ -25307,7 +25396,9 @@
       <c r="G570" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="H570" s="12"/>
+      <c r="H570" s="12">
+        <v>3</v>
+      </c>
       <c r="I570" s="12"/>
     </row>
     <row r="571" spans="1:9">
@@ -25395,130 +25486,138 @@
       <c r="I574" s="12"/>
     </row>
     <row r="575" spans="1:9">
-      <c r="A575" s="12">
+      <c r="A575" s="13">
         <v>224</v>
       </c>
-      <c r="B575" s="12" t="s">
+      <c r="B575" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="C575" s="12" t="s">
+      <c r="C575" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="D575" s="12"/>
-      <c r="E575" s="12"/>
-      <c r="F575" s="12" t="s">
+      <c r="D575" s="13">
+        <v>4</v>
+      </c>
+      <c r="E575" s="13"/>
+      <c r="F575" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="G575" s="12" t="s">
+      <c r="G575" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="H575" s="12"/>
-      <c r="I575" s="12"/>
+      <c r="H575" s="13">
+        <v>2</v>
+      </c>
+      <c r="I575" s="13"/>
     </row>
     <row r="576" spans="1:9">
-      <c r="A576" s="12">
+      <c r="A576" s="13">
         <v>224</v>
       </c>
-      <c r="B576" s="12" t="s">
+      <c r="B576" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="C576" s="12" t="s">
+      <c r="C576" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="D576" s="12"/>
-      <c r="E576" s="12"/>
-      <c r="F576" s="12" t="s">
+      <c r="D576" s="13">
+        <v>1</v>
+      </c>
+      <c r="E576" s="13"/>
+      <c r="F576" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="G576" s="12" t="s">
+      <c r="G576" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="H576" s="12"/>
-      <c r="I576" s="12"/>
+      <c r="H576" s="13">
+        <v>0</v>
+      </c>
+      <c r="I576" s="13"/>
     </row>
     <row r="577" spans="1:9">
-      <c r="A577" s="12">
+      <c r="A577" s="13">
         <v>225</v>
       </c>
-      <c r="B577" s="12" t="s">
+      <c r="B577" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="C577" s="12" t="s">
+      <c r="C577" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="D577" s="12"/>
-      <c r="E577" s="12"/>
-      <c r="F577" s="12" t="s">
+      <c r="D577" s="13"/>
+      <c r="E577" s="13"/>
+      <c r="F577" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="G577" s="12" t="s">
+      <c r="G577" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="H577" s="12"/>
-      <c r="I577" s="12"/>
+      <c r="H577" s="13"/>
+      <c r="I577" s="13"/>
     </row>
     <row r="578" spans="1:9">
-      <c r="A578" s="12">
+      <c r="A578" s="13">
         <v>225</v>
       </c>
-      <c r="B578" s="12" t="s">
+      <c r="B578" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="C578" s="12" t="s">
+      <c r="C578" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="D578" s="12"/>
-      <c r="E578" s="12"/>
-      <c r="F578" s="12" t="s">
+      <c r="D578" s="13"/>
+      <c r="E578" s="13"/>
+      <c r="F578" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="G578" s="12" t="s">
+      <c r="G578" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="H578" s="12"/>
-      <c r="I578" s="12"/>
+      <c r="H578" s="13"/>
+      <c r="I578" s="13"/>
     </row>
     <row r="579" spans="1:9">
-      <c r="A579" s="12">
+      <c r="A579" s="13">
         <v>226</v>
       </c>
-      <c r="B579" s="12" t="s">
+      <c r="B579" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="C579" s="12" t="s">
+      <c r="C579" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="D579" s="12"/>
-      <c r="E579" s="12"/>
-      <c r="F579" s="12" t="s">
+      <c r="D579" s="13"/>
+      <c r="E579" s="13"/>
+      <c r="F579" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="G579" s="12" t="s">
+      <c r="G579" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="H579" s="12"/>
-      <c r="I579" s="12"/>
+      <c r="H579" s="13"/>
+      <c r="I579" s="13"/>
     </row>
     <row r="580" spans="1:9">
-      <c r="A580" s="12">
+      <c r="A580" s="13">
         <v>226</v>
       </c>
-      <c r="B580" s="12" t="s">
+      <c r="B580" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="C580" s="12" t="s">
+      <c r="C580" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="D580" s="12"/>
-      <c r="E580" s="12"/>
-      <c r="F580" s="12" t="s">
+      <c r="D580" s="13"/>
+      <c r="E580" s="13"/>
+      <c r="F580" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="G580" s="12" t="s">
+      <c r="G580" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="H580" s="12"/>
-      <c r="I580" s="12"/>
+      <c r="H580" s="13"/>
+      <c r="I580" s="13"/>
     </row>
     <row r="581" spans="1:9">
       <c r="A581" s="10">
@@ -26065,7 +26164,7 @@
       <c r="I612" s="10"/>
     </row>
     <row r="613" spans="1:9">
-      <c r="A613" s="13">
+      <c r="A613" s="14">
         <v>259</v>
       </c>
       <c r="B613" s="8" t="s">
@@ -26088,7 +26187,7 @@
       </c>
     </row>
     <row r="614" spans="1:9">
-      <c r="A614" s="13">
+      <c r="A614" s="14">
         <v>260</v>
       </c>
       <c r="B614" s="8" t="s">
@@ -26111,7 +26210,7 @@
       </c>
     </row>
     <row r="615" spans="1:9">
-      <c r="A615" s="13">
+      <c r="A615" s="14">
         <v>261</v>
       </c>
       <c r="B615" s="8" t="s">
@@ -26134,7 +26233,7 @@
       </c>
     </row>
     <row r="616" spans="1:9">
-      <c r="A616" s="13">
+      <c r="A616" s="14">
         <v>262</v>
       </c>
       <c r="B616" s="8" t="s">
@@ -26157,7 +26256,7 @@
       </c>
     </row>
     <row r="617" spans="1:9">
-      <c r="A617" s="13">
+      <c r="A617" s="14">
         <v>263</v>
       </c>
       <c r="B617" s="8" t="s">
@@ -26180,7 +26279,7 @@
       </c>
     </row>
     <row r="618" spans="1:9">
-      <c r="A618" s="13">
+      <c r="A618" s="14">
         <v>264</v>
       </c>
       <c r="B618" s="8" t="s">
@@ -26203,7 +26302,7 @@
       </c>
     </row>
     <row r="619" spans="1:9">
-      <c r="A619" s="13">
+      <c r="A619" s="14">
         <v>265</v>
       </c>
       <c r="B619" s="8" t="s">
@@ -26226,7 +26325,7 @@
       </c>
     </row>
     <row r="620" spans="1:9">
-      <c r="A620" s="13">
+      <c r="A620" s="14">
         <v>266</v>
       </c>
       <c r="B620" s="8" t="s">
@@ -26249,7 +26348,7 @@
       </c>
     </row>
     <row r="621" spans="1:9">
-      <c r="A621" s="13">
+      <c r="A621" s="14">
         <v>267</v>
       </c>
       <c r="B621" s="8" t="s">
@@ -26272,7 +26371,7 @@
       </c>
     </row>
     <row r="622" spans="1:9">
-      <c r="A622" s="13">
+      <c r="A622" s="14">
         <v>268</v>
       </c>
       <c r="B622" s="8" t="s">
@@ -26295,7 +26394,7 @@
       </c>
     </row>
     <row r="623" spans="1:9">
-      <c r="A623" s="13">
+      <c r="A623" s="14">
         <v>269</v>
       </c>
       <c r="B623" s="8" t="s">
@@ -26318,7 +26417,7 @@
       </c>
     </row>
     <row r="624" spans="1:9">
-      <c r="A624" s="13">
+      <c r="A624" s="14">
         <v>270</v>
       </c>
       <c r="B624" s="8" t="s">
@@ -26341,7 +26440,7 @@
       </c>
     </row>
     <row r="625" spans="1:8">
-      <c r="A625" s="13">
+      <c r="A625" s="14">
         <v>271</v>
       </c>
       <c r="B625" s="8" t="s">
@@ -26364,7 +26463,7 @@
       </c>
     </row>
     <row r="626" spans="1:8">
-      <c r="A626" s="13">
+      <c r="A626" s="14">
         <v>272</v>
       </c>
       <c r="B626" s="8" t="s">
@@ -26387,7 +26486,7 @@
       </c>
     </row>
     <row r="627" spans="1:8">
-      <c r="A627" s="13">
+      <c r="A627" s="14">
         <v>273</v>
       </c>
       <c r="B627" s="8" t="s">
@@ -26553,7 +26652,7 @@
       <c r="N2" s="5">
         <v>3</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>131</v>
       </c>
       <c r="Q2" s="5"/>
@@ -26593,7 +26692,7 @@
       <c r="N3" s="5">
         <v>3</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26615,7 +26714,7 @@
       <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26637,7 +26736,7 @@
       <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26659,7 +26758,7 @@
       <c r="N6" s="5">
         <v>3</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26681,7 +26780,7 @@
       <c r="N7" s="5">
         <v>3</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="O7" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26703,7 +26802,7 @@
       <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8" s="20" t="s">
+      <c r="O8" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26741,7 +26840,7 @@
       <c r="N10" s="5">
         <v>3</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="O10" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26765,7 +26864,7 @@
       <c r="N11" s="5">
         <v>3</v>
       </c>
-      <c r="O11" s="20" t="s">
+      <c r="O11" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26789,7 +26888,7 @@
       <c r="N12" s="5">
         <v>3</v>
       </c>
-      <c r="O12" s="20" t="s">
+      <c r="O12" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26813,7 +26912,7 @@
       <c r="N13" s="5">
         <v>5</v>
       </c>
-      <c r="O13" s="20" t="s">
+      <c r="O13" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26837,7 +26936,7 @@
       <c r="N14" s="5">
         <v>3</v>
       </c>
-      <c r="O14" s="20" t="s">
+      <c r="O14" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26861,7 +26960,7 @@
       <c r="N15" s="5">
         <v>3</v>
       </c>
-      <c r="O15" s="20" t="s">
+      <c r="O15" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26899,7 +26998,7 @@
       <c r="N17" s="5">
         <v>3</v>
       </c>
-      <c r="O17" s="20" t="s">
+      <c r="O17" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26923,7 +27022,7 @@
       <c r="N18" s="5">
         <v>3</v>
       </c>
-      <c r="O18" s="20" t="s">
+      <c r="O18" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26947,7 +27046,7 @@
       <c r="N19" s="5">
         <v>3</v>
       </c>
-      <c r="O19" s="20" t="s">
+      <c r="O19" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26971,7 +27070,7 @@
       <c r="N20" s="5">
         <v>3</v>
       </c>
-      <c r="O20" s="20" t="s">
+      <c r="O20" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -26995,7 +27094,7 @@
       <c r="N21" s="5">
         <v>3</v>
       </c>
-      <c r="O21" s="20" t="s">
+      <c r="O21" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27019,7 +27118,7 @@
       <c r="N22" s="5">
         <v>3</v>
       </c>
-      <c r="O22" s="20" t="s">
+      <c r="O22" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27043,7 +27142,7 @@
       <c r="N23" s="5">
         <v>3</v>
       </c>
-      <c r="O23" s="20" t="s">
+      <c r="O23" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27067,7 +27166,7 @@
       <c r="N24" s="5">
         <v>5</v>
       </c>
-      <c r="O24" s="20" t="s">
+      <c r="O24" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27091,7 +27190,7 @@
       <c r="N25" s="5">
         <v>3</v>
       </c>
-      <c r="O25" s="20" t="s">
+      <c r="O25" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27115,7 +27214,7 @@
       <c r="N26" s="5">
         <v>3</v>
       </c>
-      <c r="O26" s="20" t="s">
+      <c r="O26" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27139,7 +27238,7 @@
       <c r="N27" s="5">
         <v>3</v>
       </c>
-      <c r="O27" s="20" t="s">
+      <c r="O27" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27163,7 +27262,7 @@
       <c r="N28" s="5">
         <v>3</v>
       </c>
-      <c r="O28" s="20" t="s">
+      <c r="O28" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27187,7 +27286,7 @@
       <c r="N29" s="5">
         <v>3</v>
       </c>
-      <c r="O29" s="20" t="s">
+      <c r="O29" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27211,7 +27310,7 @@
       <c r="N30" s="5">
         <v>3</v>
       </c>
-      <c r="O30" s="20" t="s">
+      <c r="O30" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27247,7 +27346,7 @@
       <c r="N32" s="6">
         <v>1</v>
       </c>
-      <c r="O32" s="16" t="s">
+      <c r="O32" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q32" s="6">
@@ -27272,7 +27371,7 @@
       <c r="N33" s="6">
         <v>1</v>
       </c>
-      <c r="O33" s="16" t="s">
+      <c r="O33" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q33" s="6">
@@ -27298,7 +27397,7 @@
       <c r="N34" s="6">
         <v>1</v>
       </c>
-      <c r="O34" s="16" t="s">
+      <c r="O34" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q34" s="6">
@@ -27324,7 +27423,7 @@
       <c r="N35" s="6">
         <v>3</v>
       </c>
-      <c r="O35" s="16" t="s">
+      <c r="O35" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q35" s="6">
@@ -27344,13 +27443,13 @@
         <v>166</v>
       </c>
       <c r="L36" s="6"/>
-      <c r="M36" s="18" t="s">
+      <c r="M36" s="19" t="s">
         <v>168</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
-      <c r="O36" s="16" t="s">
+      <c r="O36" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q36" s="6">
@@ -27376,7 +27475,7 @@
       <c r="N37" s="6">
         <v>3</v>
       </c>
-      <c r="O37" s="16" t="s">
+      <c r="O37" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q37" s="6">
@@ -27396,13 +27495,13 @@
         <v>170</v>
       </c>
       <c r="L38" s="6"/>
-      <c r="M38" s="18" t="s">
+      <c r="M38" s="19" t="s">
         <v>172</v>
       </c>
       <c r="N38" s="6">
         <v>3</v>
       </c>
-      <c r="O38" s="16" t="s">
+      <c r="O38" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q38" s="6">
@@ -27422,13 +27521,13 @@
         <v>170</v>
       </c>
       <c r="L39" s="6"/>
-      <c r="M39" s="16" t="s">
+      <c r="M39" s="17" t="s">
         <v>173</v>
       </c>
       <c r="N39" s="6">
         <v>3</v>
       </c>
-      <c r="O39" s="16" t="s">
+      <c r="O39" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q39" s="6">
@@ -27448,13 +27547,13 @@
         <v>175</v>
       </c>
       <c r="L40" s="6"/>
-      <c r="M40" s="16" t="s">
+      <c r="M40" s="17" t="s">
         <v>177</v>
       </c>
       <c r="N40" s="6">
         <v>3</v>
       </c>
-      <c r="O40" s="16" t="s">
+      <c r="O40" s="17" t="s">
         <v>131</v>
       </c>
       <c r="Q40" s="6">
@@ -27638,7 +27737,7 @@
       <c r="N66" s="6">
         <v>3</v>
       </c>
-      <c r="O66" s="16" t="s">
+      <c r="O66" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27660,7 +27759,7 @@
       <c r="N67" s="6">
         <v>3</v>
       </c>
-      <c r="O67" s="16" t="s">
+      <c r="O67" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27682,7 +27781,7 @@
       <c r="N68" s="6">
         <v>3</v>
       </c>
-      <c r="O68" s="16" t="s">
+      <c r="O68" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27704,7 +27803,7 @@
       <c r="N69" s="6">
         <v>3</v>
       </c>
-      <c r="O69" s="16" t="s">
+      <c r="O69" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27720,13 +27819,13 @@
         <v>166</v>
       </c>
       <c r="L70" s="6"/>
-      <c r="M70" s="18" t="s">
+      <c r="M70" s="19" t="s">
         <v>168</v>
       </c>
       <c r="N70" s="6">
         <v>3</v>
       </c>
-      <c r="O70" s="16" t="s">
+      <c r="O70" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27748,7 +27847,7 @@
       <c r="N71" s="6">
         <v>3</v>
       </c>
-      <c r="O71" s="16" t="s">
+      <c r="O71" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27770,7 +27869,7 @@
       <c r="N72" s="6">
         <v>3</v>
       </c>
-      <c r="O72" s="16" t="s">
+      <c r="O72" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27786,13 +27885,13 @@
         <v>170</v>
       </c>
       <c r="L73" s="6"/>
-      <c r="M73" s="18" t="s">
+      <c r="M73" s="19" t="s">
         <v>172</v>
       </c>
       <c r="N73" s="6">
         <v>3</v>
       </c>
-      <c r="O73" s="16" t="s">
+      <c r="O73" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27808,13 +27907,13 @@
         <v>170</v>
       </c>
       <c r="L74" s="6"/>
-      <c r="M74" s="16" t="s">
+      <c r="M74" s="17" t="s">
         <v>173</v>
       </c>
       <c r="N74" s="6">
         <v>3</v>
       </c>
-      <c r="O74" s="16" t="s">
+      <c r="O74" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27830,13 +27929,13 @@
         <v>170</v>
       </c>
       <c r="L75" s="6"/>
-      <c r="M75" s="16" t="s">
+      <c r="M75" s="17" t="s">
         <v>174</v>
       </c>
       <c r="N75" s="6">
         <v>3</v>
       </c>
-      <c r="O75" s="16" t="s">
+      <c r="O75" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27852,13 +27951,13 @@
         <v>175</v>
       </c>
       <c r="L76" s="6"/>
-      <c r="M76" s="16" t="s">
+      <c r="M76" s="17" t="s">
         <v>176</v>
       </c>
       <c r="N76" s="6">
         <v>3</v>
       </c>
-      <c r="O76" s="16" t="s">
+      <c r="O76" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27874,13 +27973,13 @@
         <v>175</v>
       </c>
       <c r="L77" s="6"/>
-      <c r="M77" s="18" t="s">
+      <c r="M77" s="19" t="s">
         <v>177</v>
       </c>
       <c r="N77" s="6">
         <v>3</v>
       </c>
-      <c r="O77" s="16" t="s">
+      <c r="O77" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27896,13 +27995,13 @@
         <v>175</v>
       </c>
       <c r="L78" s="6"/>
-      <c r="M78" s="16" t="s">
+      <c r="M78" s="17" t="s">
         <v>178</v>
       </c>
       <c r="N78" s="6">
         <v>3</v>
       </c>
-      <c r="O78" s="16" t="s">
+      <c r="O78" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -27918,13 +28017,13 @@
         <v>179</v>
       </c>
       <c r="L79" s="6"/>
-      <c r="M79" s="16" t="s">
+      <c r="M79" s="17" t="s">
         <v>180</v>
       </c>
       <c r="N79" s="6">
         <v>3</v>
       </c>
-      <c r="O79" s="16" t="s">
+      <c r="O79" s="17" t="s">
         <v>131</v>
       </c>
     </row>

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22780" windowHeight="14900" activeTab="2"/>
+    <workbookView windowWidth="23120" windowHeight="14900" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4419" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="637">
   <si>
     <t>name</t>
   </si>
@@ -4098,9 +4098,7 @@
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="10">
-        <v>1</v>
-      </c>
+      <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="10" t="s">
@@ -4114,7 +4112,9 @@
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
+      <c r="F37" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="17"/>
@@ -26615,7 +26615,9 @@
       <c r="C581" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="D581" s="10"/>
+      <c r="D581" s="10">
+        <v>0</v>
+      </c>
       <c r="E581" s="10"/>
       <c r="F581" s="10" t="s">
         <v>509</v>
@@ -26623,7 +26625,9 @@
       <c r="G581" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="H581" s="10"/>
+      <c r="H581" s="10">
+        <v>1</v>
+      </c>
       <c r="I581" s="10"/>
     </row>
     <row r="582" spans="1:9">
@@ -26636,16 +26640,24 @@
       <c r="C582" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="D582" s="10"/>
-      <c r="E582" s="10"/>
+      <c r="D582" s="10">
+        <v>1</v>
+      </c>
+      <c r="E582" s="10">
+        <v>2</v>
+      </c>
       <c r="F582" s="10" t="s">
         <v>519</v>
       </c>
       <c r="G582" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="H582" s="10"/>
-      <c r="I582" s="10"/>
+      <c r="H582" s="10">
+        <v>1</v>
+      </c>
+      <c r="I582" s="10">
+        <v>3</v>
+      </c>
     </row>
     <row r="583" spans="1:9">
       <c r="A583" s="10">
@@ -26657,16 +26669,24 @@
       <c r="C583" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D583" s="10"/>
-      <c r="E583" s="10"/>
+      <c r="D583" s="10">
+        <v>1</v>
+      </c>
+      <c r="E583" s="10">
+        <v>3</v>
+      </c>
       <c r="F583" s="10" t="s">
         <v>526</v>
       </c>
       <c r="G583" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="H583" s="10"/>
-      <c r="I583" s="10"/>
+      <c r="H583" s="10">
+        <v>1</v>
+      </c>
+      <c r="I583" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="584" spans="1:9">
       <c r="A584" s="10">
@@ -26783,7 +26803,9 @@
       <c r="C589" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="D589" s="10"/>
+      <c r="D589" s="10">
+        <v>2</v>
+      </c>
       <c r="E589" s="10"/>
       <c r="F589" s="10" t="s">
         <v>542</v>
@@ -26791,7 +26813,9 @@
       <c r="G589" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="H589" s="10"/>
+      <c r="H589" s="10">
+        <v>1</v>
+      </c>
       <c r="I589" s="10"/>
     </row>
     <row r="590" spans="1:9">
@@ -26946,15 +26970,19 @@
         <v>243</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C597" s="10"/>
+        <v>509</v>
+      </c>
+      <c r="C597" s="10" t="s">
+        <v>510</v>
+      </c>
       <c r="D597" s="10"/>
       <c r="E597" s="10"/>
       <c r="F597" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G597" s="10"/>
+        <v>519</v>
+      </c>
+      <c r="G597" s="10" t="s">
+        <v>520</v>
+      </c>
       <c r="H597" s="10"/>
       <c r="I597" s="10"/>
     </row>
@@ -26963,9 +26991,11 @@
         <v>244</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C598" s="10"/>
+        <v>526</v>
+      </c>
+      <c r="C598" s="10" t="s">
+        <v>527</v>
+      </c>
       <c r="D598" s="10"/>
       <c r="E598" s="10"/>
       <c r="F598" s="10" t="s">
@@ -27014,9 +27044,11 @@
         <v>247</v>
       </c>
       <c r="B601" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C601" s="10"/>
+        <v>517</v>
+      </c>
+      <c r="C601" s="10" t="s">
+        <v>518</v>
+      </c>
       <c r="D601" s="10"/>
       <c r="E601" s="10"/>
       <c r="F601" s="10" t="s">
@@ -27618,7 +27650,9 @@
       <c r="C630" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D630" s="10"/>
+      <c r="D630" s="10">
+        <v>3</v>
+      </c>
       <c r="E630" s="10"/>
       <c r="F630" s="10" t="s">
         <v>626</v>
@@ -27626,7 +27660,9 @@
       <c r="G630" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="H630" s="10"/>
+      <c r="H630" s="10">
+        <v>0</v>
+      </c>
       <c r="I630" s="10"/>
     </row>
     <row r="631" spans="1:9">
@@ -27639,7 +27675,9 @@
       <c r="C631" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="D631" s="10"/>
+      <c r="D631" s="10">
+        <v>3</v>
+      </c>
       <c r="E631" s="10"/>
       <c r="F631" s="10" t="s">
         <v>628</v>
@@ -27647,7 +27685,9 @@
       <c r="G631" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="H631" s="10"/>
+      <c r="H631" s="10">
+        <v>0</v>
+      </c>
       <c r="I631" s="10"/>
     </row>
     <row r="632" spans="1:9">
@@ -27655,16 +27695,24 @@
         <v>278</v>
       </c>
       <c r="B632" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C632" s="10"/>
-      <c r="D632" s="10"/>
+        <v>626</v>
+      </c>
+      <c r="C632" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="D632" s="10">
+        <v>0</v>
+      </c>
       <c r="E632" s="10"/>
       <c r="F632" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G632" s="10"/>
-      <c r="H632" s="10"/>
+        <v>625</v>
+      </c>
+      <c r="G632" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H632" s="10">
+        <v>3</v>
+      </c>
       <c r="I632" s="10"/>
     </row>
     <row r="633" spans="1:9">
@@ -27672,16 +27720,24 @@
         <v>279</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C633" s="10"/>
-      <c r="D633" s="10"/>
+        <v>87</v>
+      </c>
+      <c r="C633" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D633" s="10">
+        <v>3</v>
+      </c>
       <c r="E633" s="10"/>
       <c r="F633" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G633" s="10"/>
-      <c r="H633" s="10"/>
+        <v>625</v>
+      </c>
+      <c r="G633" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H633" s="10">
+        <v>0</v>
+      </c>
       <c r="I633" s="10"/>
     </row>
     <row r="634" spans="1:9">

--- a/public/docs/datas/matchs.xlsx
+++ b/public/docs/datas/matchs.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6290" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6296" uniqueCount="758">
   <si>
     <t>name</t>
   </si>
@@ -32866,16 +32866,24 @@
       <c r="C603" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="D603" s="13"/>
-      <c r="E603" s="13"/>
+      <c r="D603" s="13">
+        <v>0</v>
+      </c>
+      <c r="E603" s="13">
+        <v>4</v>
+      </c>
       <c r="F603" s="13" t="s">
         <v>653</v>
       </c>
       <c r="G603" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="H603" s="13"/>
-      <c r="I603" s="13"/>
+      <c r="H603" s="13">
+        <v>0</v>
+      </c>
+      <c r="I603" s="13">
+        <v>3</v>
+      </c>
     </row>
     <row r="604" spans="1:10">
       <c r="A604" s="13">
@@ -32887,7 +32895,9 @@
       <c r="C604" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="D604" s="13"/>
+      <c r="D604" s="13">
+        <v>2</v>
+      </c>
       <c r="E604" s="13"/>
       <c r="F604" s="13" t="s">
         <v>639</v>
@@ -32895,7 +32905,9 @@
       <c r="G604" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="H604" s="13"/>
+      <c r="H604" s="13">
+        <v>3</v>
+      </c>
       <c r="I604" s="13"/>
     </row>
     <row r="605" spans="1:10">
@@ -32969,15 +32981,19 @@
         <v>254</v>
       </c>
       <c r="B608" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C608" s="11"/>
+        <v>582</v>
+      </c>
+      <c r="C608" s="11" t="s">
+        <v>583</v>
+      </c>
       <c r="D608" s="11"/>
       <c r="E608" s="11"/>
       <c r="F608" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G608" s="11"/>
+        <v>639</v>
+      </c>
+      <c r="G608" s="11" t="s">
+        <v>640</v>
+      </c>
       <c r="H608" s="11"/>
       <c r="I608" s="11"/>
     </row>
@@ -33757,7 +33773,9 @@
       <c r="C642" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="D642" s="11"/>
+      <c r="D642" s="11">
+        <v>3</v>
+      </c>
       <c r="E642" s="11"/>
       <c r="F642" s="11" t="s">
         <v>453</v>
@@ -33765,7 +33783,9 @@
       <c r="G642" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="H642" s="11"/>
+      <c r="H642" s="11">
+        <v>0</v>
+      </c>
       <c r="I642" s="11"/>
     </row>
     <row r="643" spans="1:9">
@@ -33778,7 +33798,9 @@
       <c r="C643" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D643" s="11"/>
+      <c r="D643" s="11">
+        <v>3</v>
+      </c>
       <c r="E643" s="11"/>
       <c r="F643" s="11" t="s">
         <v>80</v>
@@ -33786,7 +33808,9 @@
       <c r="G643" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="H643" s="11"/>
+      <c r="H643" s="11">
+        <v>1</v>
+      </c>
       <c r="I643" s="11"/>
     </row>
     <row r="644" spans="1:9">
@@ -33799,7 +33823,9 @@
       <c r="C644" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D644" s="11"/>
+      <c r="D644" s="11">
+        <v>1</v>
+      </c>
       <c r="E644" s="11"/>
       <c r="F644" s="11" t="s">
         <v>68</v>
@@ -33807,7 +33833,9 @@
       <c r="G644" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H644" s="11"/>
+      <c r="H644" s="11">
+        <v>3</v>
+      </c>
       <c r="I644" s="11"/>
     </row>
     <row r="645" spans="1:9">
@@ -33815,15 +33843,19 @@
         <v>291</v>
       </c>
       <c r="B645" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C645" s="11"/>
+        <v>528</v>
+      </c>
+      <c r="C645" s="11" t="s">
+        <v>529</v>
+      </c>
       <c r="D645" s="11"/>
       <c r="E645" s="11"/>
       <c r="F645" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G645" s="11"/>
+        <v>471</v>
+      </c>
+      <c r="G645" s="11" t="s">
+        <v>472</v>
+      </c>
       <c r="H645" s="11"/>
       <c r="I645" s="11"/>
     </row>
@@ -33832,9 +33864,11 @@
         <v>292</v>
       </c>
       <c r="B646" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C646" s="11"/>
+        <v>104</v>
+      </c>
+      <c r="C646" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="D646" s="11"/>
       <c r="E646" s="11"/>
       <c r="F646" s="11" t="s">
@@ -33849,9 +33883,11 @@
         <v>293</v>
       </c>
       <c r="B647" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C647" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="C647" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="D647" s="11"/>
       <c r="E647" s="11"/>
       <c r="F647" s="11" t="s">
@@ -37481,7 +37517,9 @@
       <c r="C789" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="D789" s="18"/>
+      <c r="D789" s="18">
+        <v>0</v>
+      </c>
       <c r="E789" s="18"/>
       <c r="F789" s="18" t="s">
         <v>418</v>
@@ -37489,7 +37527,9 @@
       <c r="G789" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="H789" s="18"/>
+      <c r="H789" s="18">
+        <v>2</v>
+      </c>
       <c r="I789" s="18"/>
     </row>
     <row r="790" spans="1:10">
@@ -37502,7 +37542,9 @@
       <c r="C790" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="D790" s="18"/>
+      <c r="D790" s="18">
+        <v>0</v>
+      </c>
       <c r="E790" s="18"/>
       <c r="F790" s="18" t="s">
         <v>443</v>
@@ -37510,7 +37552,9 @@
       <c r="G790" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="H790" s="18"/>
+      <c r="H790" s="18">
+        <v>2</v>
+      </c>
       <c r="I790" s="18"/>
     </row>
     <row r="791" spans="1:10">
@@ -37523,7 +37567,9 @@
       <c r="C791" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D791" s="18"/>
+      <c r="D791" s="18">
+        <v>2</v>
+      </c>
       <c r="E791" s="18"/>
       <c r="F791" s="18" t="s">
         <v>719</v>
@@ -37531,7 +37577,9 @@
       <c r="G791" s="18" t="s">
         <v>720</v>
       </c>
-      <c r="H791" s="18"/>
+      <c r="H791" s="18">
+        <v>0</v>
+      </c>
       <c r="I791" s="18"/>
     </row>
     <row r="792" spans="1:10">
@@ -37802,7 +37850,9 @@
       <c r="C804" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="D804" s="11"/>
+      <c r="D804" s="11">
+        <v>1</v>
+      </c>
       <c r="E804" s="11"/>
       <c r="F804" s="11" t="s">
         <v>416</v>
@@ -37810,7 +37860,9 @@
       <c r="G804" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="H804" s="11"/>
+      <c r="H804" s="11">
+        <v>1</v>
+      </c>
       <c r="I804" s="11"/>
     </row>
     <row r="805" spans="1:9">
@@ -37823,7 +37875,9 @@
       <c r="C805" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="D805" s="11"/>
+      <c r="D805" s="11">
+        <v>1</v>
+      </c>
       <c r="E805" s="11"/>
       <c r="F805" s="11" t="s">
         <v>721</v>
@@ -37831,7 +37885,9 @@
       <c r="G805" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="H805" s="11"/>
+      <c r="H805" s="11">
+        <v>1</v>
+      </c>
       <c r="I805" s="11"/>
     </row>
     <row r="806" spans="1:9">
@@ -37844,7 +37900,9 @@
       <c r="C806" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="D806" s="11"/>
+      <c r="D806" s="11">
+        <v>2</v>
+      </c>
       <c r="E806" s="11"/>
       <c r="F806" s="11" t="s">
         <v>726</v>
@@ -37852,7 +37910,9 @@
       <c r="G806" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="H806" s="11"/>
+      <c r="H806" s="11">
+        <v>0</v>
+      </c>
       <c r="I806" s="11"/>
     </row>
     <row r="807" spans="1:9">
@@ -38030,7 +38090,9 @@
       <c r="C816" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="D816" s="11"/>
+      <c r="D816" s="11">
+        <v>1</v>
+      </c>
       <c r="E816" s="11"/>
       <c r="F816" s="11" t="s">
         <v>514</v>
@@ -38038,7 +38100,9 @@
       <c r="G816" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="H816" s="11"/>
+      <c r="H816" s="11">
+        <v>1</v>
+      </c>
       <c r="I816" s="11"/>
     </row>
     <row r="817" spans="1:9">
@@ -38051,7 +38115,9 @@
       <c r="C817" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="D817" s="11"/>
+      <c r="D817" s="11">
+        <v>0</v>
+      </c>
       <c r="E817" s="11"/>
       <c r="F817" s="11" t="s">
         <v>730</v>
@@ -38059,7 +38125,9 @@
       <c r="G817" s="11" t="s">
         <v>731</v>
       </c>
-      <c r="H817" s="11"/>
+      <c r="H817" s="11">
+        <v>2</v>
+      </c>
       <c r="I817" s="11"/>
     </row>
     <row r="818" spans="1:9">
@@ -38072,7 +38140,9 @@
       <c r="C818" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="D818" s="11"/>
+      <c r="D818" s="11">
+        <v>0</v>
+      </c>
       <c r="E818" s="11"/>
       <c r="F818" s="11" t="s">
         <v>435</v>
@@ -38080,7 +38150,9 @@
       <c r="G818" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="H818" s="11"/>
+      <c r="H818" s="11">
+        <v>2</v>
+      </c>
       <c r="I818" s="11"/>
     </row>
     <row r="819" spans="1:9">
@@ -38093,11 +38165,17 @@
       <c r="C819" s="8" t="s">
         <v>731</v>
       </c>
+      <c r="D819" s="8">
+        <v>0</v>
+      </c>
       <c r="F819" s="8" t="s">
         <v>435</v>
       </c>
       <c r="G819" s="8" t="s">
         <v>436</v>
+      </c>
+      <c r="H819" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="820" spans="1:9">
@@ -38110,11 +38188,17 @@
       <c r="C820" s="8" t="s">
         <v>729</v>
       </c>
+      <c r="D820" s="8">
+        <v>0</v>
+      </c>
       <c r="F820" s="8" t="s">
         <v>514</v>
       </c>
       <c r="G820" s="8" t="s">
         <v>515</v>
+      </c>
+      <c r="H820" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="821" spans="1:9">
@@ -38127,11 +38211,17 @@
       <c r="C821" s="8" t="s">
         <v>421</v>
       </c>
+      <c r="D821" s="8">
+        <v>2</v>
+      </c>
       <c r="F821" s="8" t="s">
         <v>424</v>
       </c>
       <c r="G821" s="8" t="s">
         <v>425</v>
+      </c>
+      <c r="H821" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="822" spans="1:9">
@@ -38321,11 +38411,17 @@
       <c r="C831" s="8" t="s">
         <v>733</v>
       </c>
+      <c r="D831" s="8">
+        <v>1</v>
+      </c>
       <c r="F831" s="8" t="s">
         <v>706</v>
       </c>
       <c r="G831" s="8" t="s">
         <v>734</v>
+      </c>
+      <c r="H831" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="832" spans="1:9">
@@ -38338,11 +38434,17 @@
       <c r="C832" s="8" t="s">
         <v>542</v>
       </c>
+      <c r="D832" s="8">
+        <v>1</v>
+      </c>
       <c r="F832" s="8" t="s">
         <v>713</v>
       </c>
       <c r="G832" s="8" t="s">
         <v>735</v>
+      </c>
+      <c r="H832" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="833" spans="1:9">
@@ -38355,11 +38457,17 @@
       <c r="C833" s="8" t="s">
         <v>737</v>
       </c>
+      <c r="D833" s="8">
+        <v>0</v>
+      </c>
       <c r="F833" s="8" t="s">
         <v>738</v>
       </c>
       <c r="G833" s="8" t="s">
         <v>739</v>
+      </c>
+      <c r="H833" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="834" spans="1:9">
@@ -38372,7 +38480,9 @@
       <c r="C834" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="D834" s="11"/>
+      <c r="D834" s="11">
+        <v>0</v>
+      </c>
       <c r="E834" s="11"/>
       <c r="F834" s="11" t="s">
         <v>738</v>
@@ -38380,7 +38490,9 @@
       <c r="G834" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="H834" s="11"/>
+      <c r="H834" s="11">
+        <v>2</v>
+      </c>
       <c r="I834" s="11"/>
     </row>
     <row r="835" spans="1:9">
@@ -38393,7 +38505,9 @@
       <c r="C835" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="D835" s="11"/>
+      <c r="D835" s="11">
+        <v>2</v>
+      </c>
       <c r="E835" s="11"/>
       <c r="F835" s="11" t="s">
         <v>706</v>
@@ -38401,7 +38515,9 @@
       <c r="G835" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="H835" s="11"/>
+      <c r="H835" s="11">
+        <v>0</v>
+      </c>
       <c r="I835" s="11"/>
     </row>
     <row r="836" spans="1:9">
@@ -38414,7 +38530,9 @@
       <c r="C836" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="D836" s="11"/>
+      <c r="D836" s="11">
+        <v>2</v>
+      </c>
       <c r="E836" s="11"/>
       <c r="F836" s="11" t="s">
         <v>736</v>
@@ -38422,7 +38540,9 @@
       <c r="G836" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="H836" s="11"/>
+      <c r="H836" s="11">
+        <v>0</v>
+      </c>
       <c r="I836" s="11"/>
     </row>
     <row r="837" spans="1:9">
